--- a/data/k-props/2026-08-24.xlsx
+++ b/data/k-props/2026-08-24.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="79">
   <si>
     <t>date</t>
   </si>
@@ -175,13 +175,16 @@
     <t>6-7</t>
   </si>
   <si>
+    <t>Kumar Rocker</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Chicago White Sox</t>
+  </si>
+  <si>
     <t>Jose Urquidy</t>
   </si>
   <si>
-    <t>Texas Rangers @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Kumar Rocker</t>
+    <t>Role unknown</t>
   </si>
   <si>
     <t>Parker Messick</t>
@@ -241,10 +244,10 @@
     <t>Cincinnati Reds @ San Francisco Giants</t>
   </si>
   <si>
+    <t>Carson Whisenhunt</t>
+  </si>
+  <si>
     <t>José Urquidy</t>
-  </si>
-  <si>
-    <t>Role unknown</t>
   </si>
 </sst>
 </file>
@@ -625,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM21"/>
+  <dimension ref="A1:AM22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -758,13 +761,13 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D2">
-        <v>124</v>
+        <v>-150</v>
       </c>
       <c r="E2">
-        <v>-159</v>
+        <v>119</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
@@ -862,10 +865,10 @@
         <v>4.5</v>
       </c>
       <c r="D3">
-        <v>-115</v>
+        <v>-113</v>
       </c>
       <c r="E3">
-        <v>-101</v>
+        <v>-110</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
@@ -960,13 +963,13 @@
         <v>47</v>
       </c>
       <c r="C4">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D4">
-        <v>124</v>
+        <v>-154</v>
       </c>
       <c r="E4">
-        <v>-155</v>
+        <v>125</v>
       </c>
       <c r="F4" t="s">
         <v>48</v>
@@ -1064,10 +1067,10 @@
         <v>4.5</v>
       </c>
       <c r="D5">
-        <v>-137</v>
+        <v>-147</v>
       </c>
       <c r="E5">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F5" t="s">
         <v>48</v>
@@ -1266,7 +1269,7 @@
         <v>6.5</v>
       </c>
       <c r="D7">
-        <v>102</v>
+        <v>-104</v>
       </c>
       <c r="E7">
         <v>-120</v>
@@ -1364,31 +1367,73 @@
         <v>54</v>
       </c>
       <c r="C8">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D8">
-        <v>-135</v>
+        <v>-128</v>
       </c>
       <c r="E8">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="F8" t="s">
         <v>55</v>
       </c>
-      <c r="G8" t="s">
-        <v>44</v>
+      <c r="G8">
+        <v>824557</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I8">
+        <v>4.9</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
       </c>
       <c r="L8">
         <v>6</v>
       </c>
+      <c r="M8">
+        <v>0.2064</v>
+      </c>
+      <c r="N8">
+        <v>5</v>
+      </c>
+      <c r="O8">
+        <v>117</v>
+      </c>
+      <c r="P8">
+        <v>4.36</v>
+      </c>
+      <c r="Q8">
+        <v>0.1966</v>
+      </c>
+      <c r="R8">
+        <v>0.369</v>
+      </c>
       <c r="S8" t="s">
-        <v>44</v>
-      </c>
-      <c r="V8" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T8">
+        <v>0.2255</v>
+      </c>
+      <c r="U8">
+        <v>0.2448</v>
+      </c>
+      <c r="V8">
+        <v>9</v>
+      </c>
+      <c r="W8">
+        <v>0.2371</v>
+      </c>
+      <c r="X8">
+        <v>0.2134</v>
+      </c>
+      <c r="Y8">
+        <v>1.0431</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1396,8 +1441,23 @@
       <c r="AC8" t="s">
         <v>44</v>
       </c>
+      <c r="AD8">
+        <v>4.8</v>
+      </c>
       <c r="AE8" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF8">
+        <v>0.2028</v>
+      </c>
+      <c r="AG8">
+        <v>1.057</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>4.8</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1408,13 +1468,13 @@
         <v>56</v>
       </c>
       <c r="C9">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D9">
-        <v>-115</v>
+        <v>-135</v>
       </c>
       <c r="E9">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="F9" t="s">
         <v>55</v>
@@ -1423,13 +1483,13 @@
         <v>824557</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1438,43 +1498,31 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>0.2064</v>
-      </c>
-      <c r="N9">
-        <v>5</v>
-      </c>
-      <c r="O9">
-        <v>117</v>
+        <v>0.2394</v>
       </c>
       <c r="P9">
-        <v>4.36</v>
-      </c>
-      <c r="Q9">
-        <v>0.1966</v>
-      </c>
-      <c r="R9">
-        <v>0.369</v>
+        <v>4.44</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2255</v>
+        <v>0.2365</v>
       </c>
       <c r="U9">
-        <v>0.2448</v>
+        <v>0.2372</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>0.2371</v>
+        <v>0.2244</v>
       </c>
       <c r="X9">
         <v>0.2134</v>
       </c>
       <c r="Y9">
-        <v>1.0431</v>
+        <v>1.0354</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1483,22 +1531,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.8</v>
+        <v>5.49</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.2028</v>
+        <v>0.2394</v>
       </c>
       <c r="AG9">
-        <v>1.057</v>
+        <v>1.1084</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>4.8</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1506,7 +1554,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10">
         <v>6.5</v>
@@ -1518,7 +1566,7 @@
         <v>125</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>823992</v>
@@ -1587,7 +1635,7 @@
         <v>7.87</v>
       </c>
       <c r="AE10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AF10">
         <v>0.2699</v>
@@ -1607,25 +1655,25 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>4.5</v>
       </c>
       <c r="D11">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E11">
-        <v>-161</v>
+        <v>-147</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>823992</v>
       </c>
       <c r="H11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I11">
         <v>4.3</v>
@@ -1708,19 +1756,19 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12">
         <v>4.5</v>
       </c>
       <c r="D12">
-        <v>-125</v>
+        <v>-118</v>
       </c>
       <c r="E12">
-        <v>105</v>
+        <v>-102</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>825041</v>
@@ -1738,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>0.2348</v>
@@ -1809,19 +1857,19 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13">
         <v>3.5</v>
       </c>
       <c r="D13">
-        <v>-150</v>
+        <v>-148</v>
       </c>
       <c r="E13">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G13">
         <v>825041</v>
@@ -1910,7 +1958,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -1919,10 +1967,10 @@
         <v>-118</v>
       </c>
       <c r="E14">
-        <v>-104</v>
+        <v>-103</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>823260</v>
@@ -2011,19 +2059,19 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15">
+        <v>5.5</v>
+      </c>
+      <c r="D15">
+        <v>124</v>
+      </c>
+      <c r="E15">
+        <v>-150</v>
+      </c>
+      <c r="F15" t="s">
         <v>67</v>
-      </c>
-      <c r="C15">
-        <v>4.5</v>
-      </c>
-      <c r="D15">
-        <v>-161</v>
-      </c>
-      <c r="E15">
-        <v>128</v>
-      </c>
-      <c r="F15" t="s">
-        <v>66</v>
       </c>
       <c r="G15">
         <v>823260</v>
@@ -2041,7 +2089,7 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>0.2641</v>
@@ -2112,19 +2160,19 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16">
         <v>4.5</v>
       </c>
       <c r="D16">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E16">
         <v>-143</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16">
         <v>824964</v>
@@ -2213,19 +2261,19 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17">
         <v>3.5</v>
       </c>
       <c r="D17">
-        <v>-120</v>
+        <v>-125</v>
       </c>
       <c r="E17">
         <v>105</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17">
         <v>824964</v>
@@ -2314,19 +2362,19 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18">
         <v>5.5</v>
       </c>
       <c r="D18">
-        <v>-158</v>
+        <v>-154</v>
       </c>
       <c r="E18">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G18">
         <v>823097</v>
@@ -2415,19 +2463,19 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C19">
         <v>7.5</v>
       </c>
       <c r="D19">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E19">
         <v>-148</v>
       </c>
       <c r="F19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G19">
         <v>823097</v>
@@ -2496,7 +2544,7 @@
         <v>7.67</v>
       </c>
       <c r="AE19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AF19">
         <v>0.2985</v>
@@ -2516,19 +2564,19 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C20">
         <v>6.5</v>
       </c>
       <c r="D20">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="E20">
-        <v>-110</v>
+        <v>-109</v>
       </c>
       <c r="F20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G20">
         <v>823183</v>
@@ -2617,22 +2665,22 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" t="s">
         <v>76</v>
       </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
       <c r="G21">
-        <v>824557</v>
+        <v>823183</v>
       </c>
       <c r="H21" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="I21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -2641,31 +2689,43 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0.2394</v>
+        <v>0.1503</v>
+      </c>
+      <c r="N21">
+        <v>5</v>
+      </c>
+      <c r="O21">
+        <v>107</v>
       </c>
       <c r="P21">
-        <v>4.44</v>
+        <v>4.78</v>
+      </c>
+      <c r="Q21">
+        <v>0.1589</v>
+      </c>
+      <c r="R21">
+        <v>0.349</v>
       </c>
       <c r="S21" t="s">
         <v>43</v>
       </c>
       <c r="T21">
-        <v>0.2365</v>
+        <v>0.3063</v>
       </c>
       <c r="U21">
-        <v>0.2372</v>
+        <v>0.2855</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>0.2244</v>
+        <v>0.2504</v>
       </c>
       <c r="X21">
         <v>0.2134</v>
       </c>
       <c r="Y21">
-        <v>1.0354</v>
+        <v>1.0463</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2674,21 +2734,101 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.49</v>
+        <v>5.03</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
       </c>
       <c r="AF21">
+        <v>0.1533</v>
+      </c>
+      <c r="AG21">
+        <v>1.4355</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>5.03</v>
+      </c>
+    </row>
+    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22">
+        <v>824557</v>
+      </c>
+      <c r="H22" t="s">
+        <v>57</v>
+      </c>
+      <c r="I22">
+        <v>4.5</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
         <v>0.2394</v>
       </c>
-      <c r="AG21">
+      <c r="P22">
+        <v>4.44</v>
+      </c>
+      <c r="S22" t="s">
+        <v>43</v>
+      </c>
+      <c r="T22">
+        <v>0.2365</v>
+      </c>
+      <c r="U22">
+        <v>0.2372</v>
+      </c>
+      <c r="V22">
+        <v>8</v>
+      </c>
+      <c r="W22">
+        <v>0.2244</v>
+      </c>
+      <c r="X22">
+        <v>0.2134</v>
+      </c>
+      <c r="Y22">
+        <v>1.0354</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD22">
+        <v>5.49</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF22">
+        <v>0.2394</v>
+      </c>
+      <c r="AG22">
         <v>1.1084</v>
       </c>
-      <c r="AH21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
         <v>5.49</v>
       </c>
     </row>

--- a/data/k-props/2026-08-24.xlsx
+++ b/data/k-props/2026-08-24.xlsx
@@ -133,36 +133,39 @@
     <t>08/24/2026</t>
   </si>
   <si>
+    <t>Drew Rasmussen</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Detroit Tigers</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Framber Valdez</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
     <t>Ranger Suarez</t>
   </si>
   <si>
     <t>Boston Red Sox @ Miami Marlins</t>
   </si>
   <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
     <t>Sandy Alcantara</t>
   </si>
   <si>
-    <t>Framber Valdez</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rays @ Detroit Tigers</t>
-  </si>
-  <si>
-    <t>Drew Rasmussen</t>
-  </si>
-  <si>
     <t>Ryan Feltner</t>
   </si>
   <si>
@@ -181,7 +184,7 @@
     <t>Texas Rangers @ Chicago White Sox</t>
   </si>
   <si>
-    <t>Jose Urquidy</t>
+    <t>José Urquidy</t>
   </si>
   <si>
     <t>Role unknown</t>
@@ -211,15 +214,15 @@
     <t>Merrill Kelly</t>
   </si>
   <si>
+    <t>Braxton Ashcraft</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ San Diego Padres</t>
+  </si>
+  <si>
     <t>Robbie Ray</t>
   </si>
   <si>
-    <t>Pittsburgh Pirates @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Braxton Ashcraft</t>
-  </si>
-  <si>
     <t>Zebby Matthews</t>
   </si>
   <si>
@@ -229,15 +232,15 @@
     <t>Jeffrey Springs</t>
   </si>
   <si>
+    <t>Zack Wheeler</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Seattle Mariners</t>
+  </si>
+  <si>
     <t>Logan Gilbert</t>
   </si>
   <si>
-    <t>Philadelphia Phillies @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Zack Wheeler</t>
-  </si>
-  <si>
     <t>Chase Burns</t>
   </si>
   <si>
@@ -245,9 +248,6 @@
   </si>
   <si>
     <t>Carson Whisenhunt</t>
-  </si>
-  <si>
-    <t>José Urquidy</t>
   </si>
 </sst>
 </file>
@@ -764,22 +764,22 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>-150</v>
+        <v>-147</v>
       </c>
       <c r="E2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>823828</v>
+        <v>824235</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -788,46 +788,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>0.242</v>
+        <v>0.2609</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="P2">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="Q2">
-        <v>0.1758</v>
+        <v>0.307</v>
       </c>
       <c r="R2">
-        <v>0.313</v>
+        <v>0.363</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2159</v>
+        <v>0.1904</v>
       </c>
       <c r="U2">
-        <v>0.2037</v>
+        <v>0.1854</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2319</v>
+        <v>0.2228</v>
       </c>
       <c r="X2">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y2">
-        <v>0.9783</v>
+        <v>0.8829</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -836,22 +836,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>4.65</v>
+        <v>4.82</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2213</v>
+        <v>0.2776</v>
       </c>
       <c r="AG2">
-        <v>1.012</v>
+        <v>0.8916</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>4.65</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -862,25 +862,25 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D3">
-        <v>-113</v>
+        <v>-154</v>
       </c>
       <c r="E3">
-        <v>-110</v>
+        <v>125</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
       <c r="G3">
-        <v>823828</v>
+        <v>824235</v>
       </c>
       <c r="H3" t="s">
         <v>42</v>
       </c>
       <c r="I3">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -889,46 +889,46 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>0.1799</v>
+        <v>0.1811</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="P3">
-        <v>4.12</v>
+        <v>4.42</v>
       </c>
       <c r="Q3">
-        <v>0.1615</v>
+        <v>0.1716</v>
       </c>
       <c r="R3">
-        <v>0.394</v>
+        <v>0.401</v>
       </c>
       <c r="S3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T3">
-        <v>0.1871</v>
+        <v>0.1633</v>
       </c>
       <c r="U3">
-        <v>0.1947</v>
+        <v>0.1619</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2142</v>
+        <v>0.1851</v>
       </c>
       <c r="X3">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y3">
-        <v>0.9792</v>
+        <v>0.9037</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -937,22 +937,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.1727</v>
+        <v>0.1773</v>
       </c>
       <c r="AG3">
-        <v>0.8771</v>
+        <v>0.7647</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -960,28 +960,28 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D4">
-        <v>-154</v>
+        <v>-150</v>
       </c>
       <c r="E4">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4">
-        <v>824235</v>
+        <v>823828</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -990,46 +990,46 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>0.1811</v>
+        <v>0.242</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="P4">
-        <v>4.42</v>
+        <v>4.12</v>
       </c>
       <c r="Q4">
-        <v>0.1716</v>
+        <v>0.1758</v>
       </c>
       <c r="R4">
-        <v>0.401</v>
+        <v>0.313</v>
       </c>
       <c r="S4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T4">
-        <v>0.1633</v>
+        <v>0.2159</v>
       </c>
       <c r="U4">
-        <v>0.1619</v>
+        <v>0.2037</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.1851</v>
+        <v>0.2319</v>
       </c>
       <c r="X4">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y4">
-        <v>0.9037</v>
+        <v>0.9783</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1038,22 +1038,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.01</v>
+        <v>4.65</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.1773</v>
+        <v>0.2213</v>
       </c>
       <c r="AG4">
-        <v>0.7653</v>
+        <v>1.0113</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.01</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1061,28 +1061,28 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>4.5</v>
       </c>
       <c r="D5">
-        <v>-147</v>
+        <v>-113</v>
       </c>
       <c r="E5">
-        <v>120</v>
+        <v>-110</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5">
-        <v>824235</v>
+        <v>823828</v>
       </c>
       <c r="H5" t="s">
         <v>42</v>
       </c>
       <c r="I5">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1091,25 +1091,25 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>0.2609</v>
+        <v>0.1799</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="P5">
-        <v>3.94</v>
+        <v>4.12</v>
       </c>
       <c r="Q5">
-        <v>0.307</v>
+        <v>0.1615</v>
       </c>
       <c r="R5">
-        <v>0.363</v>
+        <v>0.394</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
@@ -1118,19 +1118,19 @@
         <v>0.1879</v>
       </c>
       <c r="U5">
-        <v>0.1887</v>
+        <v>0.2</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2228</v>
+        <v>0.2142</v>
       </c>
       <c r="X5">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y5">
-        <v>0.9683</v>
+        <v>0.9965</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1139,22 +1139,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>5.22</v>
+        <v>4.08</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.2776</v>
+        <v>0.1727</v>
       </c>
       <c r="AG5">
-        <v>0.8807</v>
+        <v>0.8798</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>5.22</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1162,7 +1162,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>3.5</v>
@@ -1174,7 +1174,7 @@
         <v>110</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>822695</v>
@@ -1213,7 +1213,7 @@
         <v>0.381</v>
       </c>
       <c r="S6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T6">
         <v>0.2377</v>
@@ -1228,7 +1228,7 @@
         <v>0.2071</v>
       </c>
       <c r="X6">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y6">
         <v>1.02</v>
@@ -1249,7 +1249,7 @@
         <v>0.1405</v>
       </c>
       <c r="AG6">
-        <v>1.1142</v>
+        <v>1.1134</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1263,7 +1263,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7">
         <v>6.5</v>
@@ -1275,7 +1275,7 @@
         <v>-120</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>822695</v>
@@ -1314,7 +1314,7 @@
         <v>0.379</v>
       </c>
       <c r="S7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T7">
         <v>0.2288</v>
@@ -1329,7 +1329,7 @@
         <v>0.2185</v>
       </c>
       <c r="X7">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y7">
         <v>1.0247</v>
@@ -1341,22 +1341,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>6.75</v>
+        <v>6.74</v>
       </c>
       <c r="AE7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AF7">
         <v>0.2764</v>
       </c>
       <c r="AG7">
-        <v>1.0723</v>
+        <v>1.0715</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>6.75</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1364,7 +1364,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8">
         <v>4.5</v>
@@ -1376,7 +1376,7 @@
         <v>105</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8">
         <v>824557</v>
@@ -1415,7 +1415,7 @@
         <v>0.369</v>
       </c>
       <c r="S8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T8">
         <v>0.2255</v>
@@ -1430,7 +1430,7 @@
         <v>0.2371</v>
       </c>
       <c r="X8">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y8">
         <v>1.0431</v>
@@ -1451,7 +1451,7 @@
         <v>0.2028</v>
       </c>
       <c r="AG8">
-        <v>1.057</v>
+        <v>1.0563</v>
       </c>
       <c r="AH8">
         <v>0</v>
@@ -1465,7 +1465,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9">
         <v>3.5</v>
@@ -1477,13 +1477,13 @@
         <v>126</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>824557</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I9">
         <v>4.5</v>
@@ -1504,7 +1504,7 @@
         <v>4.44</v>
       </c>
       <c r="S9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T9">
         <v>0.2365</v>
@@ -1519,7 +1519,7 @@
         <v>0.2244</v>
       </c>
       <c r="X9">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y9">
         <v>1.0354</v>
@@ -1531,7 +1531,7 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>5.49</v>
+        <v>5.48</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
@@ -1540,13 +1540,13 @@
         <v>0.2394</v>
       </c>
       <c r="AG9">
-        <v>1.1084</v>
+        <v>1.1076</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>5.49</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1554,7 +1554,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10">
         <v>6.5</v>
@@ -1566,7 +1566,7 @@
         <v>125</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>823992</v>
@@ -1605,7 +1605,7 @@
         <v>0.383</v>
       </c>
       <c r="S10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T10">
         <v>0.2565</v>
@@ -1620,7 +1620,7 @@
         <v>0.2537</v>
       </c>
       <c r="X10">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y10">
         <v>1.0257</v>
@@ -1632,22 +1632,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>7.87</v>
+        <v>7.86</v>
       </c>
       <c r="AE10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AF10">
         <v>0.2699</v>
       </c>
       <c r="AG10">
-        <v>1.2024</v>
+        <v>1.2015</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>7.87</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1655,7 +1655,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11">
         <v>4.5</v>
@@ -1667,13 +1667,13 @@
         <v>-147</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>823992</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I11">
         <v>4.3</v>
@@ -1706,7 +1706,7 @@
         <v>0.336</v>
       </c>
       <c r="S11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T11">
         <v>0.2079</v>
@@ -1721,7 +1721,7 @@
         <v>0.2111</v>
       </c>
       <c r="X11">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y11">
         <v>0.9408</v>
@@ -1742,7 +1742,7 @@
         <v>0.2079</v>
       </c>
       <c r="AG11">
-        <v>0.9746</v>
+        <v>0.9739</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -1756,7 +1756,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1768,7 +1768,7 @@
         <v>-102</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>825041</v>
@@ -1807,7 +1807,7 @@
         <v>0.371</v>
       </c>
       <c r="S12" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T12">
         <v>0.1669</v>
@@ -1822,7 +1822,7 @@
         <v>0.1974</v>
       </c>
       <c r="X12">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y12">
         <v>0.9409</v>
@@ -1834,7 +1834,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
@@ -1843,13 +1843,13 @@
         <v>0.2294</v>
       </c>
       <c r="AG12">
-        <v>0.7824</v>
+        <v>0.7818</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1857,7 +1857,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C13">
         <v>3.5</v>
@@ -1869,7 +1869,7 @@
         <v>122</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>825041</v>
@@ -1908,7 +1908,7 @@
         <v>0.363</v>
       </c>
       <c r="S13" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T13">
         <v>0.2238</v>
@@ -1923,7 +1923,7 @@
         <v>0.2186</v>
       </c>
       <c r="X13">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y13">
         <v>1.0046</v>
@@ -1935,7 +1935,7 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
@@ -1944,13 +1944,13 @@
         <v>0.1552</v>
       </c>
       <c r="AG13">
-        <v>1.0489</v>
+        <v>1.0481</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1958,19 +1958,19 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14">
         <v>5.5</v>
       </c>
       <c r="D14">
-        <v>-118</v>
+        <v>124</v>
       </c>
       <c r="E14">
-        <v>-103</v>
+        <v>-150</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G14">
         <v>823260</v>
@@ -1979,7 +1979,7 @@
         <v>42</v>
       </c>
       <c r="I14">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1988,46 +1988,46 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>0.2024</v>
+        <v>0.2641</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="P14">
-        <v>4.2</v>
+        <v>4.03</v>
       </c>
       <c r="Q14">
-        <v>0.1858</v>
+        <v>0.2397</v>
       </c>
       <c r="R14">
-        <v>0.361</v>
+        <v>0.377</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T14">
-        <v>0.1962</v>
+        <v>0.1804</v>
       </c>
       <c r="U14">
-        <v>0.2165</v>
+        <v>0.1823</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>0.259</v>
+        <v>0.2161</v>
       </c>
       <c r="X14">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y14">
-        <v>1.0175</v>
+        <v>0.9882</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2036,22 +2036,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>4.22</v>
+        <v>5.13</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.1964</v>
+        <v>0.2549</v>
       </c>
       <c r="AG14">
-        <v>0.9196</v>
+        <v>0.845</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>4.22</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2059,19 +2059,19 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C15">
         <v>5.5</v>
       </c>
       <c r="D15">
-        <v>124</v>
+        <v>-118</v>
       </c>
       <c r="E15">
-        <v>-150</v>
+        <v>-103</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G15">
         <v>823260</v>
@@ -2080,55 +2080,55 @@
         <v>42</v>
       </c>
       <c r="I15">
+        <v>5.5</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15">
         <v>6</v>
       </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>5</v>
-      </c>
       <c r="M15">
-        <v>0.2641</v>
+        <v>0.2024</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="P15">
-        <v>4.03</v>
+        <v>4.2</v>
       </c>
       <c r="Q15">
-        <v>0.2397</v>
+        <v>0.1858</v>
       </c>
       <c r="R15">
-        <v>0.377</v>
+        <v>0.361</v>
       </c>
       <c r="S15" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T15">
-        <v>0.1804</v>
+        <v>0.1962</v>
       </c>
       <c r="U15">
-        <v>0.1823</v>
+        <v>0.2165</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2161</v>
+        <v>0.259</v>
       </c>
       <c r="X15">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y15">
-        <v>0.9882</v>
+        <v>1.0175</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2137,22 +2137,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.13</v>
+        <v>4.22</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.2549</v>
+        <v>0.1964</v>
       </c>
       <c r="AG15">
-        <v>0.8457</v>
+        <v>0.9189</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>5.13</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2160,7 +2160,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16">
         <v>4.5</v>
@@ -2172,7 +2172,7 @@
         <v>-143</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16">
         <v>824964</v>
@@ -2211,7 +2211,7 @@
         <v>0.361</v>
       </c>
       <c r="S16" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T16">
         <v>0.2561</v>
@@ -2226,7 +2226,7 @@
         <v>0.2138</v>
       </c>
       <c r="X16">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y16">
         <v>1.0335</v>
@@ -2238,7 +2238,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>5.98</v>
+        <v>5.97</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
@@ -2247,13 +2247,13 @@
         <v>0.1997</v>
       </c>
       <c r="AG16">
-        <v>1.2005</v>
+        <v>1.1996</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>5.98</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2261,7 +2261,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17">
         <v>3.5</v>
@@ -2273,7 +2273,7 @@
         <v>105</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17">
         <v>824964</v>
@@ -2312,7 +2312,7 @@
         <v>0.327</v>
       </c>
       <c r="S17" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T17">
         <v>0.1869</v>
@@ -2327,7 +2327,7 @@
         <v>0.221</v>
       </c>
       <c r="X17">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y17">
         <v>0.9759</v>
@@ -2348,7 +2348,7 @@
         <v>0.1501</v>
       </c>
       <c r="AG17">
-        <v>0.8759</v>
+        <v>0.8752</v>
       </c>
       <c r="AH17">
         <v>0</v>
@@ -2362,19 +2362,19 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C18">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="D18">
-        <v>-154</v>
+        <v>118</v>
       </c>
       <c r="E18">
-        <v>124</v>
+        <v>-148</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G18">
         <v>823097</v>
@@ -2383,7 +2383,7 @@
         <v>42</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2395,43 +2395,43 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.2643</v>
+        <v>0.3038</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="P18">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="Q18">
-        <v>0.2295</v>
+        <v>0.2872</v>
       </c>
       <c r="R18">
-        <v>0.379</v>
+        <v>0.32</v>
       </c>
       <c r="S18" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T18">
-        <v>0.1518</v>
+        <v>0.243</v>
       </c>
       <c r="U18">
-        <v>0.1537</v>
+        <v>0.2167</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2199</v>
+        <v>0.2248</v>
       </c>
       <c r="X18">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y18">
-        <v>0.9628</v>
+        <v>0.9998</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2440,22 +2440,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.09</v>
+        <v>7.67</v>
       </c>
       <c r="AE18" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="AF18">
-        <v>0.2511</v>
+        <v>0.2985</v>
       </c>
       <c r="AG18">
-        <v>0.7113</v>
+        <v>1.1382</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>4.09</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2463,19 +2463,19 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19">
+        <v>5.5</v>
+      </c>
+      <c r="D19">
+        <v>-154</v>
+      </c>
+      <c r="E19">
+        <v>124</v>
+      </c>
+      <c r="F19" t="s">
         <v>74</v>
-      </c>
-      <c r="C19">
-        <v>7.5</v>
-      </c>
-      <c r="D19">
-        <v>118</v>
-      </c>
-      <c r="E19">
-        <v>-148</v>
-      </c>
-      <c r="F19" t="s">
-        <v>73</v>
       </c>
       <c r="G19">
         <v>823097</v>
@@ -2484,7 +2484,7 @@
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2496,43 +2496,43 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.3038</v>
+        <v>0.2643</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="P19">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="Q19">
-        <v>0.2872</v>
+        <v>0.2295</v>
       </c>
       <c r="R19">
-        <v>0.32</v>
+        <v>0.379</v>
       </c>
       <c r="S19" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T19">
-        <v>0.243</v>
+        <v>0.1518</v>
       </c>
       <c r="U19">
-        <v>0.2167</v>
+        <v>0.1537</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2248</v>
+        <v>0.2199</v>
       </c>
       <c r="X19">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y19">
-        <v>0.9998</v>
+        <v>0.9628</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2541,22 +2541,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>7.67</v>
+        <v>4.08</v>
       </c>
       <c r="AE19" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.2985</v>
+        <v>0.2511</v>
       </c>
       <c r="AG19">
-        <v>1.1391</v>
+        <v>0.7108</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>7.67</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2564,7 +2564,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20">
         <v>6.5</v>
@@ -2576,7 +2576,7 @@
         <v>-109</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20">
         <v>823183</v>
@@ -2615,7 +2615,7 @@
         <v>0.365</v>
       </c>
       <c r="S20" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T20">
         <v>0.2085</v>
@@ -2630,7 +2630,7 @@
         <v>0.2043</v>
       </c>
       <c r="X20">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y20">
         <v>1.0236</v>
@@ -2645,13 +2645,13 @@
         <v>6.74</v>
       </c>
       <c r="AE20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AF20">
         <v>0.2953</v>
       </c>
       <c r="AG20">
-        <v>0.9771</v>
+        <v>0.9763</v>
       </c>
       <c r="AH20">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" t="s">
         <v>77</v>
-      </c>
-      <c r="F21" t="s">
-        <v>76</v>
       </c>
       <c r="G21">
         <v>823183</v>
@@ -2707,7 +2707,7 @@
         <v>0.349</v>
       </c>
       <c r="S21" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T21">
         <v>0.3063</v>
@@ -2722,7 +2722,7 @@
         <v>0.2504</v>
       </c>
       <c r="X21">
-        <v>0.2134</v>
+        <v>0.2135</v>
       </c>
       <c r="Y21">
         <v>1.0463</v>
@@ -2743,7 +2743,7 @@
         <v>0.1533</v>
       </c>
       <c r="AG21">
-        <v>1.4355</v>
+        <v>1.4344</v>
       </c>
       <c r="AH21">
         <v>0</v>
@@ -2757,16 +2757,16 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G22">
         <v>824557</v>
       </c>
       <c r="H22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I22">
         <v>4.5</v>
@@ -2787,7 +2787,7 @@
         <v>4.44</v>
       </c>
       <c r="S22" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T22">
         <v>0.2365</v>

--- a/data/k-props/2026-08-24.xlsx
+++ b/data/k-props/2026-08-24.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="81">
   <si>
     <t>date</t>
   </si>
@@ -133,39 +133,39 @@
     <t>08/24/2026</t>
   </si>
   <si>
+    <t>Sandy Alcantara</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Ranger Suarez</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>Framber Valdez</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Detroit Tigers</t>
+  </si>
+  <si>
     <t>Drew Rasmussen</t>
   </si>
   <si>
-    <t>Tampa Bay Rays @ Detroit Tigers</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Framber Valdez</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Ranger Suarez</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Sandy Alcantara</t>
-  </si>
-  <si>
     <t>Ryan Feltner</t>
   </si>
   <si>
@@ -175,79 +175,85 @@
     <t>Cade Cavalli</t>
   </si>
   <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Jose Urquidy</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Opener</t>
+  </si>
+  <si>
     <t>6-7</t>
   </si>
   <si>
     <t>Kumar Rocker</t>
   </si>
   <si>
-    <t>Texas Rangers @ Chicago White Sox</t>
+    <t>Parker Messick</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>George Klassen</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Kevin Gausman</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Merrill Kelly</t>
+  </si>
+  <si>
+    <t>Robbie Ray</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Braxton Ashcraft</t>
+  </si>
+  <si>
+    <t>Zebby Matthews</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ Athletics</t>
+  </si>
+  <si>
+    <t>Jeffrey Springs</t>
+  </si>
+  <si>
+    <t>Logan Gilbert</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>Zack Wheeler</t>
+  </si>
+  <si>
+    <t>Chase Burns</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Carson Whisenhunt</t>
   </si>
   <si>
     <t>José Urquidy</t>
   </si>
   <si>
     <t>Role unknown</t>
-  </si>
-  <si>
-    <t>Parker Messick</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>George Klassen</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Kevin Gausman</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Merrill Kelly</t>
-  </si>
-  <si>
-    <t>Braxton Ashcraft</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Robbie Ray</t>
-  </si>
-  <si>
-    <t>Zebby Matthews</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ Athletics</t>
-  </si>
-  <si>
-    <t>Jeffrey Springs</t>
-  </si>
-  <si>
-    <t>Zack Wheeler</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Logan Gilbert</t>
-  </si>
-  <si>
-    <t>Chase Burns</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Carson Whisenhunt</t>
   </si>
 </sst>
 </file>
@@ -764,22 +770,22 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>-147</v>
+        <v>100</v>
       </c>
       <c r="E2">
-        <v>120</v>
+        <v>-115</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>824235</v>
+        <v>823828</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -788,46 +794,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>0.2609</v>
+        <v>0.1799</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="P2">
-        <v>3.94</v>
+        <v>4.12</v>
       </c>
       <c r="Q2">
-        <v>0.307</v>
+        <v>0.1615</v>
       </c>
       <c r="R2">
-        <v>0.363</v>
+        <v>0.394</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.1904</v>
+        <v>0.1879</v>
       </c>
       <c r="U2">
-        <v>0.1854</v>
+        <v>0.2</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2228</v>
+        <v>0.2142</v>
       </c>
       <c r="X2">
         <v>0.2135</v>
       </c>
       <c r="Y2">
-        <v>0.8829</v>
+        <v>0.9965</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -836,22 +842,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>4.82</v>
+        <v>4.08</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2776</v>
+        <v>0.1727</v>
       </c>
       <c r="AG2">
-        <v>0.8916</v>
+        <v>0.8797</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>4.82</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -862,25 +868,25 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D3">
-        <v>-154</v>
+        <v>-141</v>
       </c>
       <c r="E3">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
       <c r="G3">
-        <v>824235</v>
+        <v>823828</v>
       </c>
       <c r="H3" t="s">
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -889,46 +895,46 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>0.1811</v>
+        <v>0.242</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="P3">
-        <v>4.42</v>
+        <v>4.12</v>
       </c>
       <c r="Q3">
-        <v>0.1716</v>
+        <v>0.1758</v>
       </c>
       <c r="R3">
-        <v>0.401</v>
+        <v>0.313</v>
       </c>
       <c r="S3" t="s">
         <v>47</v>
       </c>
       <c r="T3">
-        <v>0.1633</v>
+        <v>0.2159</v>
       </c>
       <c r="U3">
-        <v>0.1619</v>
+        <v>0.2037</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.1851</v>
+        <v>0.2319</v>
       </c>
       <c r="X3">
         <v>0.2135</v>
       </c>
       <c r="Y3">
-        <v>0.9037</v>
+        <v>0.9783</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -937,22 +943,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>3</v>
+        <v>4.65</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.1773</v>
+        <v>0.2213</v>
       </c>
       <c r="AG3">
-        <v>0.7647</v>
+        <v>1.0112</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>3</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -963,25 +969,25 @@
         <v>48</v>
       </c>
       <c r="C4">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D4">
-        <v>-150</v>
+        <v>-151</v>
       </c>
       <c r="E4">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F4" t="s">
         <v>49</v>
       </c>
       <c r="G4">
-        <v>823828</v>
+        <v>824235</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -990,46 +996,46 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>0.242</v>
+        <v>0.1811</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="P4">
-        <v>4.12</v>
+        <v>4.42</v>
       </c>
       <c r="Q4">
-        <v>0.1758</v>
+        <v>0.1716</v>
       </c>
       <c r="R4">
-        <v>0.313</v>
+        <v>0.401</v>
       </c>
       <c r="S4" t="s">
         <v>47</v>
       </c>
       <c r="T4">
-        <v>0.2159</v>
+        <v>0.1633</v>
       </c>
       <c r="U4">
-        <v>0.2037</v>
+        <v>0.1619</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2319</v>
+        <v>0.1851</v>
       </c>
       <c r="X4">
         <v>0.2135</v>
       </c>
       <c r="Y4">
-        <v>0.9783</v>
+        <v>0.9037</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1038,22 +1044,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>4.65</v>
+        <v>3</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.2213</v>
+        <v>0.1773</v>
       </c>
       <c r="AG4">
-        <v>1.0113</v>
+        <v>0.7646</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>4.65</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1067,22 +1073,22 @@
         <v>4.5</v>
       </c>
       <c r="D5">
-        <v>-113</v>
+        <v>-154</v>
       </c>
       <c r="E5">
-        <v>-110</v>
+        <v>125</v>
       </c>
       <c r="F5" t="s">
         <v>49</v>
       </c>
       <c r="G5">
-        <v>823828</v>
+        <v>824235</v>
       </c>
       <c r="H5" t="s">
         <v>42</v>
       </c>
       <c r="I5">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1091,46 +1097,46 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>0.1799</v>
+        <v>0.2609</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="P5">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="Q5">
-        <v>0.1615</v>
+        <v>0.307</v>
       </c>
       <c r="R5">
-        <v>0.394</v>
+        <v>0.363</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.1879</v>
+        <v>0.1904</v>
       </c>
       <c r="U5">
-        <v>0.2</v>
+        <v>0.1854</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2142</v>
+        <v>0.2228</v>
       </c>
       <c r="X5">
         <v>0.2135</v>
       </c>
       <c r="Y5">
-        <v>0.9965</v>
+        <v>0.8829</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1139,22 +1145,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.08</v>
+        <v>4.82</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.1727</v>
+        <v>0.2776</v>
       </c>
       <c r="AG5">
-        <v>0.8798</v>
+        <v>0.8915</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>4.08</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1168,10 +1174,10 @@
         <v>3.5</v>
       </c>
       <c r="D6">
-        <v>-120</v>
+        <v>-118</v>
       </c>
       <c r="E6">
-        <v>110</v>
+        <v>-101</v>
       </c>
       <c r="F6" t="s">
         <v>52</v>
@@ -1213,13 +1219,13 @@
         <v>0.381</v>
       </c>
       <c r="S6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2377</v>
+        <v>0.208</v>
       </c>
       <c r="U6">
-        <v>0.2367</v>
+        <v>0.2148</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1231,7 +1237,7 @@
         <v>0.2135</v>
       </c>
       <c r="Y6">
-        <v>1.02</v>
+        <v>0.9728</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1240,7 +1246,7 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>3.43</v>
+        <v>2.86</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
@@ -1249,13 +1255,13 @@
         <v>0.1405</v>
       </c>
       <c r="AG6">
-        <v>1.1134</v>
+        <v>0.9741</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>3.43</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1269,7 +1275,7 @@
         <v>6.5</v>
       </c>
       <c r="D7">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>-120</v>
@@ -1314,13 +1320,13 @@
         <v>0.379</v>
       </c>
       <c r="S7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2288</v>
+        <v>0.2426</v>
       </c>
       <c r="U7">
-        <v>0.2235</v>
+        <v>0.2203</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1332,7 +1338,7 @@
         <v>0.2135</v>
       </c>
       <c r="Y7">
-        <v>1.0247</v>
+        <v>1.0261</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1341,7 +1347,7 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>6.74</v>
+        <v>7.16</v>
       </c>
       <c r="AE7" t="s">
         <v>54</v>
@@ -1350,13 +1356,13 @@
         <v>0.2764</v>
       </c>
       <c r="AG7">
-        <v>1.0715</v>
+        <v>1.1361</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>6.74</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1367,13 +1373,13 @@
         <v>55</v>
       </c>
       <c r="C8">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D8">
-        <v>-128</v>
+        <v>-149</v>
       </c>
       <c r="E8">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="F8" t="s">
         <v>56</v>
@@ -1382,58 +1388,46 @@
         <v>824557</v>
       </c>
       <c r="H8" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="I8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.2064</v>
-      </c>
-      <c r="N8">
-        <v>5</v>
-      </c>
-      <c r="O8">
-        <v>117</v>
+        <v>0.2394</v>
       </c>
       <c r="P8">
-        <v>4.36</v>
-      </c>
-      <c r="Q8">
-        <v>0.1966</v>
-      </c>
-      <c r="R8">
-        <v>0.369</v>
+        <v>4.44</v>
       </c>
       <c r="S8" t="s">
         <v>47</v>
       </c>
       <c r="T8">
-        <v>0.2255</v>
+        <v>0.2365</v>
       </c>
       <c r="U8">
-        <v>0.2448</v>
+        <v>0.2372</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>0.2371</v>
+        <v>0.2244</v>
       </c>
       <c r="X8">
         <v>0.2135</v>
       </c>
       <c r="Y8">
-        <v>1.0431</v>
+        <v>1.0354</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1442,22 +1436,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.8</v>
+        <v>6.09</v>
       </c>
       <c r="AE8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="AF8">
-        <v>0.2028</v>
+        <v>0.2394</v>
       </c>
       <c r="AG8">
-        <v>1.0563</v>
+        <v>1.1075</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>4.8</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1465,16 +1459,16 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D9">
-        <v>-135</v>
+        <v>-128</v>
       </c>
       <c r="E9">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F9" t="s">
         <v>56</v>
@@ -1483,13 +1477,13 @@
         <v>824557</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="I9">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1498,31 +1492,43 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>0.2394</v>
+        <v>0.2064</v>
+      </c>
+      <c r="N9">
+        <v>5</v>
+      </c>
+      <c r="O9">
+        <v>117</v>
       </c>
       <c r="P9">
-        <v>4.44</v>
+        <v>4.36</v>
+      </c>
+      <c r="Q9">
+        <v>0.1966</v>
+      </c>
+      <c r="R9">
+        <v>0.369</v>
       </c>
       <c r="S9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2365</v>
+        <v>0.2419</v>
       </c>
       <c r="U9">
-        <v>0.2372</v>
+        <v>0.2489</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2244</v>
+        <v>0.2371</v>
       </c>
       <c r="X9">
         <v>0.2135</v>
       </c>
       <c r="Y9">
-        <v>1.0354</v>
+        <v>1.0901</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1531,22 +1537,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>5.48</v>
+        <v>5.38</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.2394</v>
+        <v>0.2028</v>
       </c>
       <c r="AG9">
-        <v>1.1076</v>
+        <v>1.1327</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>5.48</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1554,19 +1560,19 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="D10">
-        <v>-156</v>
+        <v>117</v>
       </c>
       <c r="E10">
-        <v>125</v>
+        <v>-150</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>823992</v>
@@ -1635,13 +1641,13 @@
         <v>7.86</v>
       </c>
       <c r="AE10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="AF10">
         <v>0.2699</v>
       </c>
       <c r="AG10">
-        <v>1.2015</v>
+        <v>1.2014</v>
       </c>
       <c r="AH10">
         <v>0</v>
@@ -1667,7 +1673,7 @@
         <v>-147</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>823992</v>
@@ -1742,7 +1748,7 @@
         <v>0.2079</v>
       </c>
       <c r="AG11">
-        <v>0.9739</v>
+        <v>0.9738</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -1762,10 +1768,10 @@
         <v>4.5</v>
       </c>
       <c r="D12">
-        <v>-118</v>
+        <v>-113</v>
       </c>
       <c r="E12">
-        <v>-102</v>
+        <v>-105</v>
       </c>
       <c r="F12" t="s">
         <v>65</v>
@@ -1843,7 +1849,7 @@
         <v>0.2294</v>
       </c>
       <c r="AG12">
-        <v>0.7818</v>
+        <v>0.7817</v>
       </c>
       <c r="AH12">
         <v>0</v>
@@ -1863,10 +1869,10 @@
         <v>3.5</v>
       </c>
       <c r="D13">
-        <v>-148</v>
+        <v>-136</v>
       </c>
       <c r="E13">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F13" t="s">
         <v>65</v>
@@ -1944,7 +1950,7 @@
         <v>0.1552</v>
       </c>
       <c r="AG13">
-        <v>1.0481</v>
+        <v>1.048</v>
       </c>
       <c r="AH13">
         <v>0</v>
@@ -1964,10 +1970,10 @@
         <v>5.5</v>
       </c>
       <c r="D14">
-        <v>124</v>
+        <v>-118</v>
       </c>
       <c r="E14">
-        <v>-150</v>
+        <v>-102</v>
       </c>
       <c r="F14" t="s">
         <v>68</v>
@@ -1979,55 +1985,55 @@
         <v>42</v>
       </c>
       <c r="I14">
+        <v>5.5</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14">
         <v>6</v>
       </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>5</v>
-      </c>
       <c r="M14">
-        <v>0.2641</v>
+        <v>0.2024</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="P14">
-        <v>4.03</v>
+        <v>4.2</v>
       </c>
       <c r="Q14">
-        <v>0.2397</v>
+        <v>0.1858</v>
       </c>
       <c r="R14">
-        <v>0.377</v>
+        <v>0.361</v>
       </c>
       <c r="S14" t="s">
         <v>47</v>
       </c>
       <c r="T14">
-        <v>0.1804</v>
+        <v>0.1962</v>
       </c>
       <c r="U14">
-        <v>0.1823</v>
+        <v>0.2165</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2161</v>
+        <v>0.259</v>
       </c>
       <c r="X14">
         <v>0.2135</v>
       </c>
       <c r="Y14">
-        <v>0.9882</v>
+        <v>1.0175</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2036,22 +2042,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>5.13</v>
+        <v>4.22</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.2549</v>
+        <v>0.1964</v>
       </c>
       <c r="AG14">
-        <v>0.845</v>
+        <v>0.9188</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>5.13</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2065,10 +2071,10 @@
         <v>5.5</v>
       </c>
       <c r="D15">
-        <v>-118</v>
+        <v>125</v>
       </c>
       <c r="E15">
-        <v>-103</v>
+        <v>-150</v>
       </c>
       <c r="F15" t="s">
         <v>68</v>
@@ -2080,7 +2086,7 @@
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2092,43 +2098,43 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.2024</v>
+        <v>0.2641</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="P15">
-        <v>4.2</v>
+        <v>4.03</v>
       </c>
       <c r="Q15">
-        <v>0.1858</v>
+        <v>0.2397</v>
       </c>
       <c r="R15">
-        <v>0.361</v>
+        <v>0.377</v>
       </c>
       <c r="S15" t="s">
         <v>47</v>
       </c>
       <c r="T15">
-        <v>0.1962</v>
+        <v>0.1804</v>
       </c>
       <c r="U15">
-        <v>0.2165</v>
+        <v>0.1823</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>0.259</v>
+        <v>0.2161</v>
       </c>
       <c r="X15">
         <v>0.2135</v>
       </c>
       <c r="Y15">
-        <v>1.0175</v>
+        <v>0.9882</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2137,22 +2143,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>4.22</v>
+        <v>5.13</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.1964</v>
+        <v>0.2549</v>
       </c>
       <c r="AG15">
-        <v>0.9189</v>
+        <v>0.8449</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>4.22</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2166,7 +2172,7 @@
         <v>4.5</v>
       </c>
       <c r="D16">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="E16">
         <v>-143</v>
@@ -2247,7 +2253,7 @@
         <v>0.1997</v>
       </c>
       <c r="AG16">
-        <v>1.1996</v>
+        <v>1.1994</v>
       </c>
       <c r="AH16">
         <v>0</v>
@@ -2267,7 +2273,7 @@
         <v>3.5</v>
       </c>
       <c r="D17">
-        <v>-125</v>
+        <v>-128</v>
       </c>
       <c r="E17">
         <v>105</v>
@@ -2348,7 +2354,7 @@
         <v>0.1501</v>
       </c>
       <c r="AG17">
-        <v>0.8752</v>
+        <v>0.8751</v>
       </c>
       <c r="AH17">
         <v>0</v>
@@ -2365,13 +2371,13 @@
         <v>73</v>
       </c>
       <c r="C18">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="D18">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E18">
-        <v>-148</v>
+        <v>-140</v>
       </c>
       <c r="F18" t="s">
         <v>74</v>
@@ -2383,7 +2389,7 @@
         <v>42</v>
       </c>
       <c r="I18">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2395,43 +2401,43 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.3038</v>
+        <v>0.2643</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="P18">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="Q18">
-        <v>0.2872</v>
+        <v>0.2295</v>
       </c>
       <c r="R18">
-        <v>0.32</v>
+        <v>0.379</v>
       </c>
       <c r="S18" t="s">
         <v>47</v>
       </c>
       <c r="T18">
-        <v>0.243</v>
+        <v>0.1518</v>
       </c>
       <c r="U18">
-        <v>0.2167</v>
+        <v>0.1537</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2248</v>
+        <v>0.2199</v>
       </c>
       <c r="X18">
         <v>0.2135</v>
       </c>
       <c r="Y18">
-        <v>0.9998</v>
+        <v>0.9628</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2440,22 +2446,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>7.67</v>
+        <v>4.08</v>
       </c>
       <c r="AE18" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="AF18">
-        <v>0.2985</v>
+        <v>0.2511</v>
       </c>
       <c r="AG18">
-        <v>1.1382</v>
+        <v>0.7107</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>7.67</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2466,13 +2472,13 @@
         <v>75</v>
       </c>
       <c r="C19">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="D19">
-        <v>-154</v>
+        <v>124</v>
       </c>
       <c r="E19">
-        <v>124</v>
+        <v>-148</v>
       </c>
       <c r="F19" t="s">
         <v>74</v>
@@ -2484,7 +2490,7 @@
         <v>42</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2496,43 +2502,43 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.2643</v>
+        <v>0.3038</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="P19">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="Q19">
-        <v>0.2295</v>
+        <v>0.2872</v>
       </c>
       <c r="R19">
-        <v>0.379</v>
+        <v>0.32</v>
       </c>
       <c r="S19" t="s">
         <v>47</v>
       </c>
       <c r="T19">
-        <v>0.1518</v>
+        <v>0.243</v>
       </c>
       <c r="U19">
-        <v>0.1537</v>
+        <v>0.2167</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2199</v>
+        <v>0.2248</v>
       </c>
       <c r="X19">
         <v>0.2135</v>
       </c>
       <c r="Y19">
-        <v>0.9628</v>
+        <v>0.9998</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2541,22 +2547,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>4.08</v>
+        <v>7.67</v>
       </c>
       <c r="AE19" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="AF19">
-        <v>0.2511</v>
+        <v>0.2985</v>
       </c>
       <c r="AG19">
-        <v>0.7108</v>
+        <v>1.1381</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>4.08</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2645,13 +2651,13 @@
         <v>6.74</v>
       </c>
       <c r="AE20" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AF20">
         <v>0.2953</v>
       </c>
       <c r="AG20">
-        <v>0.9763</v>
+        <v>0.9762</v>
       </c>
       <c r="AH20">
         <v>0</v>
@@ -2667,6 +2673,15 @@
       <c r="B21" t="s">
         <v>78</v>
       </c>
+      <c r="C21">
+        <v>4.5</v>
+      </c>
+      <c r="D21">
+        <v>105</v>
+      </c>
+      <c r="E21">
+        <v>-117</v>
+      </c>
       <c r="F21" t="s">
         <v>77</v>
       </c>
@@ -2686,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>0.1503</v>
@@ -2743,7 +2758,7 @@
         <v>0.1533</v>
       </c>
       <c r="AG21">
-        <v>1.4344</v>
+        <v>1.4343</v>
       </c>
       <c r="AH21">
         <v>0</v>
@@ -2757,7 +2772,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s">
         <v>56</v>
@@ -2766,7 +2781,7 @@
         <v>824557</v>
       </c>
       <c r="H22" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="I22">
         <v>4.5</v>

--- a/data/k-props/2026-08-24.xlsx
+++ b/data/k-props/2026-08-24.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="80">
   <si>
     <t>date</t>
   </si>
@@ -154,51 +154,51 @@
     <t>Ranger Suarez</t>
   </si>
   <si>
+    <t>Framber Valdez</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Detroit Tigers</t>
+  </si>
+  <si>
+    <t>Drew Rasmussen</t>
+  </si>
+  <si>
+    <t>Ryan Feltner</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Washington Nationals</t>
+  </si>
+  <si>
+    <t>Cade Cavalli</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Kumar Rocker</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Jose Urquidy</t>
+  </si>
+  <si>
+    <t>Role unknown</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Parker Messick</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Los Angeles Angels</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
-    <t>Framber Valdez</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rays @ Detroit Tigers</t>
-  </si>
-  <si>
-    <t>Drew Rasmussen</t>
-  </si>
-  <si>
-    <t>Ryan Feltner</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Washington Nationals</t>
-  </si>
-  <si>
-    <t>Cade Cavalli</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Jose Urquidy</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Opener</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Kumar Rocker</t>
-  </si>
-  <si>
-    <t>Parker Messick</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Los Angeles Angels</t>
-  </si>
-  <si>
     <t>George Klassen</t>
   </si>
   <si>
@@ -251,9 +251,6 @@
   </si>
   <si>
     <t>José Urquidy</t>
-  </si>
-  <si>
-    <t>Role unknown</t>
   </si>
 </sst>
 </file>
@@ -770,10 +767,10 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E2">
-        <v>-115</v>
+        <v>-125</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
@@ -830,7 +827,7 @@
         <v>0.2142</v>
       </c>
       <c r="X2">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y2">
         <v>0.9965</v>
@@ -842,7 +839,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -851,13 +848,13 @@
         <v>0.1727</v>
       </c>
       <c r="AG2">
-        <v>0.8797</v>
+        <v>0.8721</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -871,10 +868,10 @@
         <v>4.5</v>
       </c>
       <c r="D3">
-        <v>-141</v>
+        <v>-135</v>
       </c>
       <c r="E3">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
@@ -916,13 +913,13 @@
         <v>0.313</v>
       </c>
       <c r="S3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T3">
-        <v>0.2159</v>
+        <v>0.2163</v>
       </c>
       <c r="U3">
-        <v>0.2037</v>
+        <v>0.199</v>
       </c>
       <c r="V3">
         <v>9</v>
@@ -931,10 +928,10 @@
         <v>0.2319</v>
       </c>
       <c r="X3">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y3">
-        <v>0.9783</v>
+        <v>0.916</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -943,7 +940,7 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>4.65</v>
+        <v>4.32</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
@@ -952,13 +949,13 @@
         <v>0.2213</v>
       </c>
       <c r="AG3">
-        <v>1.0112</v>
+        <v>1.0041</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>4.65</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -966,19 +963,19 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4">
         <v>3.5</v>
       </c>
       <c r="D4">
-        <v>-151</v>
+        <v>-145</v>
       </c>
       <c r="E4">
         <v>124</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>824235</v>
@@ -1017,13 +1014,13 @@
         <v>0.401</v>
       </c>
       <c r="S4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T4">
-        <v>0.1633</v>
+        <v>0.1881</v>
       </c>
       <c r="U4">
-        <v>0.1619</v>
+        <v>0.1822</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -1032,10 +1029,10 @@
         <v>0.1851</v>
       </c>
       <c r="X4">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y4">
-        <v>0.9037</v>
+        <v>0.88</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1044,7 +1041,7 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
@@ -1053,13 +1050,13 @@
         <v>0.1773</v>
       </c>
       <c r="AG4">
-        <v>0.7646</v>
+        <v>0.8734</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1067,19 +1064,19 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D5">
-        <v>-154</v>
+        <v>135</v>
       </c>
       <c r="E5">
-        <v>125</v>
+        <v>-160</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>824235</v>
@@ -1133,7 +1130,7 @@
         <v>0.2228</v>
       </c>
       <c r="X5">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y5">
         <v>0.8829</v>
@@ -1145,7 +1142,7 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
@@ -1154,13 +1151,13 @@
         <v>0.2776</v>
       </c>
       <c r="AG5">
-        <v>0.8915</v>
+        <v>0.8838</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1168,7 +1165,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>3.5</v>
@@ -1180,7 +1177,7 @@
         <v>-101</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6">
         <v>822695</v>
@@ -1234,7 +1231,7 @@
         <v>0.2071</v>
       </c>
       <c r="X6">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y6">
         <v>0.9728</v>
@@ -1246,7 +1243,7 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
@@ -1255,13 +1252,13 @@
         <v>0.1405</v>
       </c>
       <c r="AG6">
-        <v>0.9741</v>
+        <v>0.9657</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1269,19 +1266,19 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7">
         <v>6.5</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E7">
-        <v>-120</v>
+        <v>-119</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7">
         <v>822695</v>
@@ -1335,7 +1332,7 @@
         <v>0.2185</v>
       </c>
       <c r="X7">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y7">
         <v>1.0261</v>
@@ -1347,22 +1344,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>7.16</v>
+        <v>7.1</v>
       </c>
       <c r="AE7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AF7">
         <v>0.2764</v>
       </c>
       <c r="AG7">
-        <v>1.1361</v>
+        <v>1.1263</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>7.16</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1370,64 +1367,76 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8">
+        <v>4.5</v>
+      </c>
+      <c r="D8">
+        <v>-123</v>
+      </c>
+      <c r="E8">
+        <v>102</v>
+      </c>
+      <c r="F8" t="s">
         <v>55</v>
-      </c>
-      <c r="C8">
-        <v>3.5</v>
-      </c>
-      <c r="D8">
-        <v>-149</v>
-      </c>
-      <c r="E8">
-        <v>126</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
       </c>
       <c r="G8">
         <v>824557</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.2394</v>
+        <v>0.2064</v>
+      </c>
+      <c r="N8">
+        <v>5</v>
+      </c>
+      <c r="O8">
+        <v>117</v>
       </c>
       <c r="P8">
-        <v>4.44</v>
+        <v>4.36</v>
+      </c>
+      <c r="Q8">
+        <v>0.1966</v>
+      </c>
+      <c r="R8">
+        <v>0.369</v>
       </c>
       <c r="S8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2365</v>
+        <v>0.2419</v>
       </c>
       <c r="U8">
-        <v>0.2372</v>
+        <v>0.2489</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2244</v>
+        <v>0.2371</v>
       </c>
       <c r="X8">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y8">
-        <v>1.0354</v>
+        <v>1.0901</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1436,22 +1445,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>6.09</v>
+        <v>5.33</v>
       </c>
       <c r="AE8" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.2394</v>
+        <v>0.2028</v>
       </c>
       <c r="AG8">
-        <v>1.1075</v>
+        <v>1.1229</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>6.09</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1459,76 +1468,64 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C9">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D9">
-        <v>-128</v>
+        <v>-143</v>
       </c>
       <c r="E9">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9">
         <v>824557</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>6</v>
       </c>
       <c r="M9">
-        <v>0.2064</v>
-      </c>
-      <c r="N9">
-        <v>5</v>
-      </c>
-      <c r="O9">
-        <v>117</v>
+        <v>0.2394</v>
       </c>
       <c r="P9">
-        <v>4.36</v>
-      </c>
-      <c r="Q9">
-        <v>0.1966</v>
-      </c>
-      <c r="R9">
-        <v>0.369</v>
+        <v>4.44</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2419</v>
+        <v>0.2411</v>
       </c>
       <c r="U9">
-        <v>0.2489</v>
+        <v>0.2406</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2371</v>
+        <v>0.2244</v>
       </c>
       <c r="X9">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y9">
-        <v>1.0901</v>
+        <v>1.0766</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1537,22 +1534,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>5.38</v>
+        <v>6.4</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="AF9">
-        <v>0.2028</v>
+        <v>0.2394</v>
       </c>
       <c r="AG9">
-        <v>1.1327</v>
+        <v>1.1192</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>5.38</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1560,7 +1557,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C10">
         <v>7.5</v>
@@ -1572,7 +1569,7 @@
         <v>-150</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>823992</v>
@@ -1611,7 +1608,7 @@
         <v>0.383</v>
       </c>
       <c r="S10" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="T10">
         <v>0.2565</v>
@@ -1626,7 +1623,7 @@
         <v>0.2537</v>
       </c>
       <c r="X10">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y10">
         <v>1.0257</v>
@@ -1638,22 +1635,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>7.86</v>
+        <v>7.79</v>
       </c>
       <c r="AE10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AF10">
         <v>0.2699</v>
       </c>
       <c r="AG10">
-        <v>1.2014</v>
+        <v>1.191</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>7.86</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1673,7 +1670,7 @@
         <v>-147</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>823992</v>
@@ -1712,7 +1709,7 @@
         <v>0.336</v>
       </c>
       <c r="S11" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="T11">
         <v>0.2079</v>
@@ -1727,7 +1724,7 @@
         <v>0.2111</v>
       </c>
       <c r="X11">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y11">
         <v>0.9408</v>
@@ -1739,7 +1736,7 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
@@ -1748,13 +1745,13 @@
         <v>0.2079</v>
       </c>
       <c r="AG11">
-        <v>0.9738</v>
+        <v>0.9654</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1768,7 +1765,7 @@
         <v>4.5</v>
       </c>
       <c r="D12">
-        <v>-113</v>
+        <v>-105</v>
       </c>
       <c r="E12">
         <v>-105</v>
@@ -1813,7 +1810,7 @@
         <v>0.371</v>
       </c>
       <c r="S12" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="T12">
         <v>0.1669</v>
@@ -1828,7 +1825,7 @@
         <v>0.1974</v>
       </c>
       <c r="X12">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y12">
         <v>0.9409</v>
@@ -1840,7 +1837,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
@@ -1849,13 +1846,13 @@
         <v>0.2294</v>
       </c>
       <c r="AG12">
-        <v>0.7817</v>
+        <v>0.775</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1869,10 +1866,10 @@
         <v>3.5</v>
       </c>
       <c r="D13">
-        <v>-136</v>
+        <v>-138</v>
       </c>
       <c r="E13">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F13" t="s">
         <v>65</v>
@@ -1914,7 +1911,7 @@
         <v>0.363</v>
       </c>
       <c r="S13" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="T13">
         <v>0.2238</v>
@@ -1929,7 +1926,7 @@
         <v>0.2186</v>
       </c>
       <c r="X13">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y13">
         <v>1.0046</v>
@@ -1941,7 +1938,7 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
@@ -1950,13 +1947,13 @@
         <v>0.1552</v>
       </c>
       <c r="AG13">
-        <v>1.048</v>
+        <v>1.0389</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1970,7 +1967,7 @@
         <v>5.5</v>
       </c>
       <c r="D14">
-        <v>-118</v>
+        <v>-114</v>
       </c>
       <c r="E14">
         <v>-102</v>
@@ -2015,7 +2012,7 @@
         <v>0.361</v>
       </c>
       <c r="S14" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="T14">
         <v>0.1962</v>
@@ -2030,7 +2027,7 @@
         <v>0.259</v>
       </c>
       <c r="X14">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y14">
         <v>1.0175</v>
@@ -2042,7 +2039,7 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>4.22</v>
+        <v>4.18</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
@@ -2051,13 +2048,13 @@
         <v>0.1964</v>
       </c>
       <c r="AG14">
-        <v>0.9188</v>
+        <v>0.9109</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>4.22</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2116,7 +2113,7 @@
         <v>0.377</v>
       </c>
       <c r="S15" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="T15">
         <v>0.1804</v>
@@ -2131,7 +2128,7 @@
         <v>0.2161</v>
       </c>
       <c r="X15">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y15">
         <v>0.9882</v>
@@ -2143,7 +2140,7 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.13</v>
+        <v>5.08</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
@@ -2152,13 +2149,13 @@
         <v>0.2549</v>
       </c>
       <c r="AG15">
-        <v>0.8449</v>
+        <v>0.8376</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>5.13</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2172,10 +2169,10 @@
         <v>4.5</v>
       </c>
       <c r="D16">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E16">
-        <v>-143</v>
+        <v>-148</v>
       </c>
       <c r="F16" t="s">
         <v>71</v>
@@ -2217,7 +2214,7 @@
         <v>0.361</v>
       </c>
       <c r="S16" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="T16">
         <v>0.2561</v>
@@ -2232,7 +2229,7 @@
         <v>0.2138</v>
       </c>
       <c r="X16">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y16">
         <v>1.0335</v>
@@ -2244,7 +2241,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>5.97</v>
+        <v>5.92</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
@@ -2253,13 +2250,13 @@
         <v>0.1997</v>
       </c>
       <c r="AG16">
-        <v>1.1994</v>
+        <v>1.1891</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>5.97</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2273,10 +2270,10 @@
         <v>3.5</v>
       </c>
       <c r="D17">
-        <v>-128</v>
+        <v>-130</v>
       </c>
       <c r="E17">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F17" t="s">
         <v>71</v>
@@ -2318,13 +2315,13 @@
         <v>0.327</v>
       </c>
       <c r="S17" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T17">
-        <v>0.1869</v>
+        <v>0.1944</v>
       </c>
       <c r="U17">
-        <v>0.1852</v>
+        <v>0.1867</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -2333,10 +2330,10 @@
         <v>0.221</v>
       </c>
       <c r="X17">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y17">
-        <v>0.9759</v>
+        <v>0.9436</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2345,7 +2342,7 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
@@ -2354,13 +2351,13 @@
         <v>0.1501</v>
       </c>
       <c r="AG17">
-        <v>0.8751</v>
+        <v>0.9023</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2419,7 +2416,7 @@
         <v>0.379</v>
       </c>
       <c r="S18" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="T18">
         <v>0.1518</v>
@@ -2434,7 +2431,7 @@
         <v>0.2199</v>
       </c>
       <c r="X18">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y18">
         <v>0.9628</v>
@@ -2446,7 +2443,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
@@ -2455,13 +2452,13 @@
         <v>0.2511</v>
       </c>
       <c r="AG18">
-        <v>0.7107</v>
+        <v>0.7046</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2520,7 +2517,7 @@
         <v>0.32</v>
       </c>
       <c r="S19" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="T19">
         <v>0.243</v>
@@ -2535,7 +2532,7 @@
         <v>0.2248</v>
       </c>
       <c r="X19">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y19">
         <v>0.9998</v>
@@ -2547,22 +2544,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>7.67</v>
+        <v>7.6</v>
       </c>
       <c r="AE19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AF19">
         <v>0.2985</v>
       </c>
       <c r="AG19">
-        <v>1.1381</v>
+        <v>1.1283</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>7.67</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2576,10 +2573,10 @@
         <v>6.5</v>
       </c>
       <c r="D20">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="E20">
-        <v>-109</v>
+        <v>-115</v>
       </c>
       <c r="F20" t="s">
         <v>77</v>
@@ -2621,7 +2618,7 @@
         <v>0.365</v>
       </c>
       <c r="S20" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="T20">
         <v>0.2085</v>
@@ -2636,7 +2633,7 @@
         <v>0.2043</v>
       </c>
       <c r="X20">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y20">
         <v>1.0236</v>
@@ -2648,7 +2645,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>6.74</v>
+        <v>6.68</v>
       </c>
       <c r="AE20" t="s">
         <v>58</v>
@@ -2657,13 +2654,13 @@
         <v>0.2953</v>
       </c>
       <c r="AG20">
-        <v>0.9762</v>
+        <v>0.9678</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>6.74</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2722,7 +2719,7 @@
         <v>0.349</v>
       </c>
       <c r="S21" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="T21">
         <v>0.3063</v>
@@ -2737,7 +2734,7 @@
         <v>0.2504</v>
       </c>
       <c r="X21">
-        <v>0.2135</v>
+        <v>0.2154</v>
       </c>
       <c r="Y21">
         <v>1.0463</v>
@@ -2749,7 +2746,7 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.03</v>
+        <v>4.99</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
@@ -2758,13 +2755,13 @@
         <v>0.1533</v>
       </c>
       <c r="AG21">
-        <v>1.4343</v>
+        <v>1.4219</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>5.03</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2775,13 +2772,13 @@
         <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G22">
         <v>824557</v>
       </c>
       <c r="H22" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="I22">
         <v>4.5</v>
@@ -2802,7 +2799,7 @@
         <v>4.44</v>
       </c>
       <c r="S22" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="T22">
         <v>0.2365</v>

--- a/data/k-props/2026-08-24.xlsx
+++ b/data/k-props/2026-08-24.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="79">
   <si>
     <t>date</t>
   </si>
@@ -133,36 +133,36 @@
     <t>08/24/2026</t>
   </si>
   <si>
+    <t>Drew Rasmussen</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Detroit Tigers</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Framber Valdez</t>
+  </si>
+  <si>
+    <t>Ranger Suarez</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Miami Marlins</t>
+  </si>
+  <si>
     <t>Sandy Alcantara</t>
   </si>
   <si>
-    <t>Boston Red Sox @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Ranger Suarez</t>
-  </si>
-  <si>
-    <t>Framber Valdez</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rays @ Detroit Tigers</t>
-  </si>
-  <si>
-    <t>Drew Rasmussen</t>
-  </si>
-  <si>
     <t>Ryan Feltner</t>
   </si>
   <si>
@@ -181,7 +181,7 @@
     <t>Texas Rangers @ Chicago White Sox</t>
   </si>
   <si>
-    <t>Jose Urquidy</t>
+    <t>José Urquidy</t>
   </si>
   <si>
     <t>Role unknown</t>
@@ -214,15 +214,15 @@
     <t>Merrill Kelly</t>
   </si>
   <si>
+    <t>Braxton Ashcraft</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ San Diego Padres</t>
+  </si>
+  <si>
     <t>Robbie Ray</t>
   </si>
   <si>
-    <t>Pittsburgh Pirates @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Braxton Ashcraft</t>
-  </si>
-  <si>
     <t>Zebby Matthews</t>
   </si>
   <si>
@@ -232,15 +232,15 @@
     <t>Jeffrey Springs</t>
   </si>
   <si>
+    <t>Zack Wheeler</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Seattle Mariners</t>
+  </si>
+  <si>
     <t>Logan Gilbert</t>
   </si>
   <si>
-    <t>Philadelphia Phillies @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Zack Wheeler</t>
-  </si>
-  <si>
     <t>Chase Burns</t>
   </si>
   <si>
@@ -248,9 +248,6 @@
   </si>
   <si>
     <t>Carson Whisenhunt</t>
-  </si>
-  <si>
-    <t>José Urquidy</t>
   </si>
 </sst>
 </file>
@@ -764,25 +761,25 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D2">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="E2">
-        <v>-125</v>
+        <v>-160</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>823828</v>
+        <v>824235</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -791,46 +788,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>0.1799</v>
+        <v>0.2609</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="P2">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="Q2">
-        <v>0.1615</v>
+        <v>0.307</v>
       </c>
       <c r="R2">
-        <v>0.394</v>
+        <v>0.363</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.1879</v>
+        <v>0.1904</v>
       </c>
       <c r="U2">
-        <v>0.2</v>
+        <v>0.1854</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2142</v>
+        <v>0.2228</v>
       </c>
       <c r="X2">
         <v>0.2154</v>
       </c>
       <c r="Y2">
-        <v>0.9965</v>
+        <v>0.8829</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -839,22 +836,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>4.05</v>
+        <v>4.78</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.1727</v>
+        <v>0.2776</v>
       </c>
       <c r="AG2">
-        <v>0.8721</v>
+        <v>0.884</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>4.05</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -865,25 +862,25 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D3">
-        <v>-135</v>
+        <v>-145</v>
       </c>
       <c r="E3">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
       <c r="G3">
-        <v>823828</v>
+        <v>824235</v>
       </c>
       <c r="H3" t="s">
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -892,46 +889,46 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>0.242</v>
+        <v>0.1811</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="P3">
-        <v>4.12</v>
+        <v>4.42</v>
       </c>
       <c r="Q3">
-        <v>0.1758</v>
+        <v>0.1716</v>
       </c>
       <c r="R3">
-        <v>0.313</v>
+        <v>0.401</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.2163</v>
+        <v>0.1881</v>
       </c>
       <c r="U3">
-        <v>0.199</v>
+        <v>0.1822</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2319</v>
+        <v>0.1851</v>
       </c>
       <c r="X3">
         <v>0.2154</v>
       </c>
       <c r="Y3">
-        <v>0.916</v>
+        <v>0.88</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -940,22 +937,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>4.32</v>
+        <v>3.34</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.2213</v>
+        <v>0.1773</v>
       </c>
       <c r="AG3">
-        <v>1.0041</v>
+        <v>0.8735</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>4.32</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -966,25 +963,25 @@
         <v>47</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D4">
-        <v>-145</v>
+        <v>-135</v>
       </c>
       <c r="E4">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F4" t="s">
         <v>48</v>
       </c>
       <c r="G4">
-        <v>824235</v>
+        <v>823828</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -993,46 +990,46 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>0.1811</v>
+        <v>0.242</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="P4">
-        <v>4.42</v>
+        <v>4.12</v>
       </c>
       <c r="Q4">
-        <v>0.1716</v>
+        <v>0.1758</v>
       </c>
       <c r="R4">
-        <v>0.401</v>
+        <v>0.313</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.1881</v>
+        <v>0.2163</v>
       </c>
       <c r="U4">
-        <v>0.1822</v>
+        <v>0.199</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.1851</v>
+        <v>0.2319</v>
       </c>
       <c r="X4">
         <v>0.2154</v>
       </c>
       <c r="Y4">
-        <v>0.88</v>
+        <v>0.916</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1041,22 +1038,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.34</v>
+        <v>4.32</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.1773</v>
+        <v>0.2213</v>
       </c>
       <c r="AG4">
-        <v>0.8734</v>
+        <v>1.0043</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.34</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1067,25 +1064,25 @@
         <v>49</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D5">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="E5">
-        <v>-160</v>
+        <v>-125</v>
       </c>
       <c r="F5" t="s">
         <v>48</v>
       </c>
       <c r="G5">
-        <v>824235</v>
+        <v>823828</v>
       </c>
       <c r="H5" t="s">
         <v>42</v>
       </c>
       <c r="I5">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1094,46 +1091,46 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>0.2609</v>
+        <v>0.1799</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="P5">
-        <v>3.94</v>
+        <v>4.12</v>
       </c>
       <c r="Q5">
-        <v>0.307</v>
+        <v>0.1615</v>
       </c>
       <c r="R5">
-        <v>0.363</v>
+        <v>0.394</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.1904</v>
+        <v>0.1879</v>
       </c>
       <c r="U5">
-        <v>0.1854</v>
+        <v>0.2</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2228</v>
+        <v>0.2142</v>
       </c>
       <c r="X5">
         <v>0.2154</v>
       </c>
       <c r="Y5">
-        <v>0.8829</v>
+        <v>0.9965</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1142,22 +1139,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.78</v>
+        <v>4.05</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.2776</v>
+        <v>0.1727</v>
       </c>
       <c r="AG5">
-        <v>0.8838</v>
+        <v>0.8722</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>4.78</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1252,7 +1249,7 @@
         <v>0.1405</v>
       </c>
       <c r="AG6">
-        <v>0.9657</v>
+        <v>0.9658</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1353,7 +1350,7 @@
         <v>0.2764</v>
       </c>
       <c r="AG7">
-        <v>1.1263</v>
+        <v>1.1265</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1454,7 +1451,7 @@
         <v>0.2028</v>
       </c>
       <c r="AG8">
-        <v>1.1229</v>
+        <v>1.123</v>
       </c>
       <c r="AH8">
         <v>0</v>
@@ -1543,7 +1540,7 @@
         <v>0.2394</v>
       </c>
       <c r="AG9">
-        <v>1.1192</v>
+        <v>1.1193</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -1644,7 +1641,7 @@
         <v>0.2699</v>
       </c>
       <c r="AG10">
-        <v>1.191</v>
+        <v>1.1912</v>
       </c>
       <c r="AH10">
         <v>0</v>
@@ -1736,7 +1733,7 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
@@ -1745,13 +1742,13 @@
         <v>0.2079</v>
       </c>
       <c r="AG11">
-        <v>0.9654</v>
+        <v>0.9655</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1846,7 +1843,7 @@
         <v>0.2294</v>
       </c>
       <c r="AG12">
-        <v>0.775</v>
+        <v>0.7751</v>
       </c>
       <c r="AH12">
         <v>0</v>
@@ -1947,7 +1944,7 @@
         <v>0.1552</v>
       </c>
       <c r="AG13">
-        <v>1.0389</v>
+        <v>1.0391</v>
       </c>
       <c r="AH13">
         <v>0</v>
@@ -1967,10 +1964,10 @@
         <v>5.5</v>
       </c>
       <c r="D14">
-        <v>-114</v>
+        <v>125</v>
       </c>
       <c r="E14">
-        <v>-102</v>
+        <v>-150</v>
       </c>
       <c r="F14" t="s">
         <v>68</v>
@@ -1982,7 +1979,7 @@
         <v>42</v>
       </c>
       <c r="I14">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1994,43 +1991,43 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.2024</v>
+        <v>0.2641</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="P14">
-        <v>4.2</v>
+        <v>4.03</v>
       </c>
       <c r="Q14">
-        <v>0.1858</v>
+        <v>0.2397</v>
       </c>
       <c r="R14">
-        <v>0.361</v>
+        <v>0.377</v>
       </c>
       <c r="S14" t="s">
         <v>61</v>
       </c>
       <c r="T14">
-        <v>0.1962</v>
+        <v>0.1804</v>
       </c>
       <c r="U14">
-        <v>0.2165</v>
+        <v>0.1823</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>0.259</v>
+        <v>0.2161</v>
       </c>
       <c r="X14">
         <v>0.2154</v>
       </c>
       <c r="Y14">
-        <v>1.0175</v>
+        <v>0.9882</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2039,22 +2036,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>4.18</v>
+        <v>5.08</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.1964</v>
+        <v>0.2549</v>
       </c>
       <c r="AG14">
-        <v>0.9109</v>
+        <v>0.8378</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>4.18</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2068,10 +2065,10 @@
         <v>5.5</v>
       </c>
       <c r="D15">
-        <v>125</v>
+        <v>-114</v>
       </c>
       <c r="E15">
-        <v>-150</v>
+        <v>-102</v>
       </c>
       <c r="F15" t="s">
         <v>68</v>
@@ -2083,7 +2080,7 @@
         <v>42</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2095,43 +2092,43 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.2641</v>
+        <v>0.2024</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="P15">
-        <v>4.03</v>
+        <v>4.2</v>
       </c>
       <c r="Q15">
-        <v>0.2397</v>
+        <v>0.1858</v>
       </c>
       <c r="R15">
-        <v>0.377</v>
+        <v>0.361</v>
       </c>
       <c r="S15" t="s">
         <v>61</v>
       </c>
       <c r="T15">
-        <v>0.1804</v>
+        <v>0.1962</v>
       </c>
       <c r="U15">
-        <v>0.1823</v>
+        <v>0.2165</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2161</v>
+        <v>0.259</v>
       </c>
       <c r="X15">
         <v>0.2154</v>
       </c>
       <c r="Y15">
-        <v>0.9882</v>
+        <v>1.0175</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2140,22 +2137,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.08</v>
+        <v>4.18</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.2549</v>
+        <v>0.1964</v>
       </c>
       <c r="AG15">
-        <v>0.8376</v>
+        <v>0.911</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>5.08</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2250,7 +2247,7 @@
         <v>0.1997</v>
       </c>
       <c r="AG16">
-        <v>1.1891</v>
+        <v>1.1893</v>
       </c>
       <c r="AH16">
         <v>0</v>
@@ -2351,7 +2348,7 @@
         <v>0.1501</v>
       </c>
       <c r="AG17">
-        <v>0.9023</v>
+        <v>0.9024</v>
       </c>
       <c r="AH17">
         <v>0</v>
@@ -2368,13 +2365,13 @@
         <v>73</v>
       </c>
       <c r="C18">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="D18">
         <v>124</v>
       </c>
       <c r="E18">
-        <v>-140</v>
+        <v>-148</v>
       </c>
       <c r="F18" t="s">
         <v>74</v>
@@ -2386,7 +2383,7 @@
         <v>42</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2398,43 +2395,43 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.2643</v>
+        <v>0.3038</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="P18">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="Q18">
-        <v>0.2295</v>
+        <v>0.2872</v>
       </c>
       <c r="R18">
-        <v>0.379</v>
+        <v>0.32</v>
       </c>
       <c r="S18" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="T18">
-        <v>0.1518</v>
+        <v>0.2424</v>
       </c>
       <c r="U18">
-        <v>0.1537</v>
+        <v>0.2236</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2199</v>
+        <v>0.2248</v>
       </c>
       <c r="X18">
         <v>0.2154</v>
       </c>
       <c r="Y18">
-        <v>0.9628</v>
+        <v>0.9919</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2443,22 +2440,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.05</v>
+        <v>7.52</v>
       </c>
       <c r="AE18" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AF18">
-        <v>0.2511</v>
+        <v>0.2985</v>
       </c>
       <c r="AG18">
-        <v>0.7046</v>
+        <v>1.1253</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>4.05</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2469,13 +2466,13 @@
         <v>75</v>
       </c>
       <c r="C19">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="D19">
         <v>124</v>
       </c>
       <c r="E19">
-        <v>-148</v>
+        <v>-140</v>
       </c>
       <c r="F19" t="s">
         <v>74</v>
@@ -2487,7 +2484,7 @@
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2499,43 +2496,43 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.3038</v>
+        <v>0.2643</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="P19">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="Q19">
-        <v>0.2872</v>
+        <v>0.2295</v>
       </c>
       <c r="R19">
-        <v>0.32</v>
+        <v>0.379</v>
       </c>
       <c r="S19" t="s">
         <v>61</v>
       </c>
       <c r="T19">
-        <v>0.243</v>
+        <v>0.1518</v>
       </c>
       <c r="U19">
-        <v>0.2167</v>
+        <v>0.1537</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2248</v>
+        <v>0.2199</v>
       </c>
       <c r="X19">
         <v>0.2154</v>
       </c>
       <c r="Y19">
-        <v>0.9998</v>
+        <v>0.9628</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2544,22 +2541,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>7.6</v>
+        <v>4.05</v>
       </c>
       <c r="AE19" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.2985</v>
+        <v>0.2511</v>
       </c>
       <c r="AG19">
-        <v>1.1283</v>
+        <v>0.7047</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>7.6</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2654,7 +2651,7 @@
         <v>0.2953</v>
       </c>
       <c r="AG20">
-        <v>0.9678</v>
+        <v>0.9679</v>
       </c>
       <c r="AH20">
         <v>0</v>
@@ -2755,7 +2752,7 @@
         <v>0.1533</v>
       </c>
       <c r="AG21">
-        <v>1.4219</v>
+        <v>1.4221</v>
       </c>
       <c r="AH21">
         <v>0</v>
@@ -2769,7 +2766,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="F22" t="s">
         <v>55</v>

--- a/data/k-props/2026-08-24.xlsx
+++ b/data/k-props/2026-08-24.xlsx
@@ -196,55 +196,55 @@
     <t>Cleveland Guardians @ Los Angeles Angels</t>
   </si>
   <si>
+    <t>George Klassen</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Kevin Gausman</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Merrill Kelly</t>
+  </si>
+  <si>
+    <t>Braxton Ashcraft</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Robbie Ray</t>
+  </si>
+  <si>
+    <t>Zebby Matthews</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ Athletics</t>
+  </si>
+  <si>
+    <t>Jeffrey Springs</t>
+  </si>
+  <si>
+    <t>Zack Wheeler</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>Logan Gilbert</t>
+  </si>
+  <si>
+    <t>Chase Burns</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ San Francisco Giants</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>George Klassen</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Kevin Gausman</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Merrill Kelly</t>
-  </si>
-  <si>
-    <t>Braxton Ashcraft</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Robbie Ray</t>
-  </si>
-  <si>
-    <t>Zebby Matthews</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ Athletics</t>
-  </si>
-  <si>
-    <t>Jeffrey Springs</t>
-  </si>
-  <si>
-    <t>Zack Wheeler</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Logan Gilbert</t>
-  </si>
-  <si>
-    <t>Chase Burns</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ San Francisco Giants</t>
   </si>
   <si>
     <t>Carson Whisenhunt</t>
@@ -779,7 +779,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -791,22 +791,22 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>0.2609</v>
+        <v>0.2597</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="P2">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="Q2">
-        <v>0.307</v>
+        <v>0.28</v>
       </c>
       <c r="R2">
-        <v>0.363</v>
+        <v>0.333</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
@@ -824,7 +824,7 @@
         <v>0.2228</v>
       </c>
       <c r="X2">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y2">
         <v>0.8829</v>
@@ -836,22 +836,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>4.78</v>
+        <v>4.42</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2776</v>
+        <v>0.2665</v>
       </c>
       <c r="AG2">
-        <v>0.884</v>
+        <v>0.8713</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>4.78</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -892,22 +892,22 @@
         <v>5</v>
       </c>
       <c r="M3">
-        <v>0.1811</v>
+        <v>0.1762</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="P3">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="Q3">
-        <v>0.1716</v>
+        <v>0.1532</v>
       </c>
       <c r="R3">
-        <v>0.401</v>
+        <v>0.383</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
@@ -925,7 +925,7 @@
         <v>0.1851</v>
       </c>
       <c r="X3">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y3">
         <v>0.88</v>
@@ -937,22 +937,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>3.34</v>
+        <v>3.07</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.1773</v>
+        <v>0.1674</v>
       </c>
       <c r="AG3">
-        <v>0.8735</v>
+        <v>0.861</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>3.34</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -981,7 +981,7 @@
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -993,7 +993,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>0.242</v>
+        <v>0.2402</v>
       </c>
       <c r="N4">
         <v>5</v>
@@ -1002,10 +1002,10 @@
         <v>91</v>
       </c>
       <c r="P4">
-        <v>4.12</v>
+        <v>4.15</v>
       </c>
       <c r="Q4">
-        <v>0.1758</v>
+        <v>0.1429</v>
       </c>
       <c r="R4">
         <v>0.313</v>
@@ -1026,7 +1026,7 @@
         <v>0.2319</v>
       </c>
       <c r="X4">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y4">
         <v>0.916</v>
@@ -1038,22 +1038,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>4.32</v>
+        <v>3.99</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.2213</v>
+        <v>0.2097</v>
       </c>
       <c r="AG4">
-        <v>1.0043</v>
+        <v>0.9899</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>4.32</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1082,7 +1082,7 @@
         <v>42</v>
       </c>
       <c r="I5">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1094,22 +1094,22 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>0.1799</v>
+        <v>0.18</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="P5">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="Q5">
-        <v>0.1615</v>
+        <v>0.1579</v>
       </c>
       <c r="R5">
-        <v>0.394</v>
+        <v>0.363</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
@@ -1127,7 +1127,7 @@
         <v>0.2142</v>
       </c>
       <c r="X5">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y5">
         <v>0.9965</v>
@@ -1139,22 +1139,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.05</v>
+        <v>3.89</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.1727</v>
+        <v>0.172</v>
       </c>
       <c r="AG5">
-        <v>0.8722</v>
+        <v>0.8598</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>4.05</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1183,7 +1183,7 @@
         <v>42</v>
       </c>
       <c r="I6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1195,22 +1195,22 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>0.1569</v>
+        <v>0.1607</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="P6">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
       <c r="Q6">
-        <v>0.1138</v>
+        <v>0.1193</v>
       </c>
       <c r="R6">
-        <v>0.381</v>
+        <v>0.353</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
@@ -1228,7 +1228,7 @@
         <v>0.2071</v>
       </c>
       <c r="X6">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y6">
         <v>0.9728</v>
@@ -1240,22 +1240,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.1405</v>
+        <v>0.1461</v>
       </c>
       <c r="AG6">
-        <v>0.9658</v>
+        <v>0.952</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1284,7 +1284,7 @@
         <v>42</v>
       </c>
       <c r="I7">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1296,22 +1296,22 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>0.27</v>
+        <v>0.2684</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="P7">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
       <c r="Q7">
-        <v>0.2869</v>
+        <v>0.3148</v>
       </c>
       <c r="R7">
-        <v>0.379</v>
+        <v>0.351</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
@@ -1329,7 +1329,7 @@
         <v>0.2185</v>
       </c>
       <c r="X7">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y7">
         <v>1.0261</v>
@@ -1341,22 +1341,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>7.1</v>
+        <v>7.08</v>
       </c>
       <c r="AE7" t="s">
         <v>53</v>
       </c>
       <c r="AF7">
-        <v>0.2764</v>
+        <v>0.2847</v>
       </c>
       <c r="AG7">
-        <v>1.1265</v>
+        <v>1.1104</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>7.1</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1430,7 +1430,7 @@
         <v>0.2371</v>
       </c>
       <c r="X8">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y8">
         <v>1.0901</v>
@@ -1442,7 +1442,7 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>5.33</v>
+        <v>5.26</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
@@ -1451,13 +1451,13 @@
         <v>0.2028</v>
       </c>
       <c r="AG8">
-        <v>1.123</v>
+        <v>1.107</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>5.33</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1519,7 +1519,7 @@
         <v>0.2244</v>
       </c>
       <c r="X9">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y9">
         <v>1.0766</v>
@@ -1531,7 +1531,7 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>6.4</v>
+        <v>6.31</v>
       </c>
       <c r="AE9" t="s">
         <v>58</v>
@@ -1540,13 +1540,13 @@
         <v>0.2394</v>
       </c>
       <c r="AG9">
-        <v>1.1193</v>
+        <v>1.1033</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>6.4</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1605,13 +1605,13 @@
         <v>0.383</v>
       </c>
       <c r="S10" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2565</v>
+        <v>0.311</v>
       </c>
       <c r="U10">
-        <v>0.2453</v>
+        <v>0.2783</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1620,10 +1620,10 @@
         <v>0.2537</v>
       </c>
       <c r="X10">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y10">
-        <v>1.0257</v>
+        <v>1.0953</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1632,7 +1632,7 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>7.79</v>
+        <v>9.95</v>
       </c>
       <c r="AE10" t="s">
         <v>53</v>
@@ -1641,13 +1641,13 @@
         <v>0.2699</v>
       </c>
       <c r="AG10">
-        <v>1.1912</v>
+        <v>1.4234</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>7.79</v>
+        <v>9.95</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1655,7 +1655,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>4.5</v>
@@ -1673,7 +1673,7 @@
         <v>823992</v>
       </c>
       <c r="H11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I11">
         <v>4.3</v>
@@ -1706,13 +1706,13 @@
         <v>0.336</v>
       </c>
       <c r="S11" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="T11">
-        <v>0.2079</v>
+        <v>0.1573</v>
       </c>
       <c r="U11">
-        <v>0.1844</v>
+        <v>0.1607</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1721,10 +1721,10 @@
         <v>0.2111</v>
       </c>
       <c r="X11">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y11">
-        <v>0.9408</v>
+        <v>0.88</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1733,7 +1733,7 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>3.82</v>
+        <v>2.66</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
@@ -1742,13 +1742,13 @@
         <v>0.2079</v>
       </c>
       <c r="AG11">
-        <v>0.9655</v>
+        <v>0.72</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>3.82</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1756,7 +1756,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1768,7 +1768,7 @@
         <v>-105</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>825041</v>
@@ -1807,13 +1807,13 @@
         <v>0.371</v>
       </c>
       <c r="S12" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="T12">
-        <v>0.1669</v>
+        <v>0.1747</v>
       </c>
       <c r="U12">
-        <v>0.1676</v>
+        <v>0.1722</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1822,10 +1822,10 @@
         <v>0.1974</v>
       </c>
       <c r="X12">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y12">
-        <v>0.9409</v>
+        <v>0.88</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1834,7 +1834,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
@@ -1843,13 +1843,13 @@
         <v>0.2294</v>
       </c>
       <c r="AG12">
-        <v>0.7751</v>
+        <v>0.7994</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1857,7 +1857,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C13">
         <v>3.5</v>
@@ -1869,7 +1869,7 @@
         <v>114</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G13">
         <v>825041</v>
@@ -1908,13 +1908,13 @@
         <v>0.363</v>
       </c>
       <c r="S13" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2238</v>
+        <v>0.2204</v>
       </c>
       <c r="U13">
-        <v>0.2222</v>
+        <v>0.2197</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1923,10 +1923,10 @@
         <v>0.2186</v>
       </c>
       <c r="X13">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y13">
-        <v>1.0046</v>
+        <v>0.9794</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1935,7 +1935,7 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>3.98</v>
+        <v>3.77</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
@@ -1944,13 +1944,13 @@
         <v>0.1552</v>
       </c>
       <c r="AG13">
-        <v>1.0391</v>
+        <v>1.0085</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>3.98</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1958,7 +1958,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -1970,7 +1970,7 @@
         <v>-150</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>823260</v>
@@ -2009,13 +2009,13 @@
         <v>0.377</v>
       </c>
       <c r="S14" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="T14">
-        <v>0.1804</v>
+        <v>0.1869</v>
       </c>
       <c r="U14">
-        <v>0.1823</v>
+        <v>0.1886</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -2024,10 +2024,10 @@
         <v>0.2161</v>
       </c>
       <c r="X14">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y14">
-        <v>0.9882</v>
+        <v>1.0085</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2036,7 +2036,7 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>5.08</v>
+        <v>5.3</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
@@ -2045,13 +2045,13 @@
         <v>0.2549</v>
       </c>
       <c r="AG14">
-        <v>0.8378</v>
+        <v>0.8556</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>5.08</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2059,7 +2059,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15">
         <v>5.5</v>
@@ -2071,7 +2071,7 @@
         <v>-102</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G15">
         <v>823260</v>
@@ -2110,13 +2110,13 @@
         <v>0.361</v>
       </c>
       <c r="S15" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="T15">
-        <v>0.1962</v>
+        <v>0.2783</v>
       </c>
       <c r="U15">
-        <v>0.2165</v>
+        <v>0.264</v>
       </c>
       <c r="V15">
         <v>9</v>
@@ -2125,10 +2125,10 @@
         <v>0.259</v>
       </c>
       <c r="X15">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y15">
-        <v>1.0175</v>
+        <v>1.0952</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2137,22 +2137,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>4.18</v>
+        <v>6.3</v>
       </c>
       <c r="AE15" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="AF15">
         <v>0.1964</v>
       </c>
       <c r="AG15">
-        <v>0.911</v>
+        <v>1.2737</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>4.18</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2160,7 +2160,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16">
         <v>4.5</v>
@@ -2172,7 +2172,7 @@
         <v>-148</v>
       </c>
       <c r="F16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G16">
         <v>824964</v>
@@ -2211,13 +2211,13 @@
         <v>0.361</v>
       </c>
       <c r="S16" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="T16">
-        <v>0.2561</v>
+        <v>0.2071</v>
       </c>
       <c r="U16">
-        <v>0.2291</v>
+        <v>0.2029</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -2226,10 +2226,10 @@
         <v>0.2138</v>
       </c>
       <c r="X16">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y16">
-        <v>1.0335</v>
+        <v>1.0204</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2238,7 +2238,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>5.92</v>
+        <v>4.66</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
@@ -2247,13 +2247,13 @@
         <v>0.1997</v>
       </c>
       <c r="AG16">
-        <v>1.1893</v>
+        <v>0.9479</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>5.92</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2261,7 +2261,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C17">
         <v>3.5</v>
@@ -2273,7 +2273,7 @@
         <v>115</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G17">
         <v>824964</v>
@@ -2327,7 +2327,7 @@
         <v>0.221</v>
       </c>
       <c r="X17">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y17">
         <v>0.9436</v>
@@ -2339,7 +2339,7 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
@@ -2348,13 +2348,13 @@
         <v>0.1501</v>
       </c>
       <c r="AG17">
-        <v>0.9024</v>
+        <v>0.8895</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2362,7 +2362,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18">
         <v>7.5</v>
@@ -2374,7 +2374,7 @@
         <v>-148</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G18">
         <v>823097</v>
@@ -2428,7 +2428,7 @@
         <v>0.2248</v>
       </c>
       <c r="X18">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y18">
         <v>0.9919</v>
@@ -2440,7 +2440,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>7.52</v>
+        <v>7.41</v>
       </c>
       <c r="AE18" t="s">
         <v>53</v>
@@ -2449,13 +2449,13 @@
         <v>0.2985</v>
       </c>
       <c r="AG18">
-        <v>1.1253</v>
+        <v>1.1092</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>7.52</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2463,7 +2463,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19">
         <v>6.5</v>
@@ -2475,7 +2475,7 @@
         <v>-140</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G19">
         <v>823097</v>
@@ -2514,7 +2514,7 @@
         <v>0.379</v>
       </c>
       <c r="S19" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="T19">
         <v>0.1518</v>
@@ -2529,10 +2529,10 @@
         <v>0.2199</v>
       </c>
       <c r="X19">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y19">
-        <v>0.9628</v>
+        <v>0.9256</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2541,7 +2541,7 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
@@ -2550,13 +2550,13 @@
         <v>0.2511</v>
       </c>
       <c r="AG19">
-        <v>0.7047</v>
+        <v>0.6946</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2564,7 +2564,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20">
         <v>6.5</v>
@@ -2576,7 +2576,7 @@
         <v>-115</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G20">
         <v>823183</v>
@@ -2615,7 +2615,7 @@
         <v>0.365</v>
       </c>
       <c r="S20" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="T20">
         <v>0.2085</v>
@@ -2630,7 +2630,7 @@
         <v>0.2043</v>
       </c>
       <c r="X20">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y20">
         <v>1.0236</v>
@@ -2642,7 +2642,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>6.68</v>
+        <v>6.59</v>
       </c>
       <c r="AE20" t="s">
         <v>58</v>
@@ -2651,13 +2651,13 @@
         <v>0.2953</v>
       </c>
       <c r="AG20">
-        <v>0.9679</v>
+        <v>0.9541</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>6.68</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2677,7 +2677,7 @@
         <v>-117</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G21">
         <v>823183</v>
@@ -2716,13 +2716,13 @@
         <v>0.349</v>
       </c>
       <c r="S21" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="T21">
-        <v>0.3063</v>
+        <v>0.3211</v>
       </c>
       <c r="U21">
-        <v>0.2855</v>
+        <v>0.2873</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2731,10 +2731,10 @@
         <v>0.2504</v>
       </c>
       <c r="X21">
-        <v>0.2154</v>
+        <v>0.2185</v>
       </c>
       <c r="Y21">
-        <v>1.0463</v>
+        <v>1.0671</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2743,7 +2743,7 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>4.99</v>
+        <v>5.25</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
@@ -2752,13 +2752,13 @@
         <v>0.1533</v>
       </c>
       <c r="AG21">
-        <v>1.4221</v>
+        <v>1.4694</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>4.99</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2796,7 +2796,7 @@
         <v>4.44</v>
       </c>
       <c r="S22" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="T22">
         <v>0.2365</v>

--- a/data/k-props/2026-08-24.xlsx
+++ b/data/k-props/2026-08-24.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="80">
   <si>
     <t>date</t>
   </si>
@@ -184,70 +184,73 @@
     <t>José Urquidy</t>
   </si>
   <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Parker Messick</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>George Klassen</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Kevin Gausman</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Merrill Kelly</t>
+  </si>
+  <si>
+    <t>Braxton Ashcraft</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Robbie Ray</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Zebby Matthews</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ Athletics</t>
+  </si>
+  <si>
+    <t>Jeffrey Springs</t>
+  </si>
+  <si>
+    <t>Zack Wheeler</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>Logan Gilbert</t>
+  </si>
+  <si>
+    <t>Chase Burns</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Carson Whisenhunt</t>
+  </si>
+  <si>
     <t>Role unknown</t>
   </si>
   <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Parker Messick</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>George Klassen</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Kevin Gausman</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Merrill Kelly</t>
-  </si>
-  <si>
-    <t>Braxton Ashcraft</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Robbie Ray</t>
-  </si>
-  <si>
-    <t>Zebby Matthews</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ Athletics</t>
-  </si>
-  <si>
-    <t>Jeffrey Springs</t>
-  </si>
-  <si>
-    <t>Zack Wheeler</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Logan Gilbert</t>
-  </si>
-  <si>
-    <t>Chase Burns</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ San Francisco Giants</t>
-  </si>
-  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Carson Whisenhunt</t>
   </si>
 </sst>
 </file>
@@ -779,7 +782,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -791,22 +794,22 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>0.2597</v>
+        <v>0.26</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="P2">
         <v>3.92</v>
       </c>
       <c r="Q2">
-        <v>0.28</v>
+        <v>0.2793</v>
       </c>
       <c r="R2">
-        <v>0.333</v>
+        <v>0.357</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
@@ -824,7 +827,7 @@
         <v>0.2228</v>
       </c>
       <c r="X2">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y2">
         <v>0.8829</v>
@@ -836,22 +839,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>4.42</v>
+        <v>4.51</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2665</v>
+        <v>0.2669</v>
       </c>
       <c r="AG2">
-        <v>0.8713</v>
+        <v>0.8698</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>4.42</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -880,7 +883,7 @@
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -892,22 +895,22 @@
         <v>5</v>
       </c>
       <c r="M3">
-        <v>0.1762</v>
+        <v>0.1737</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="P3">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="Q3">
-        <v>0.1532</v>
+        <v>0.1397</v>
       </c>
       <c r="R3">
-        <v>0.383</v>
+        <v>0.405</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
@@ -925,7 +928,7 @@
         <v>0.1851</v>
       </c>
       <c r="X3">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y3">
         <v>0.88</v>
@@ -937,22 +940,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.1674</v>
+        <v>0.1599</v>
       </c>
       <c r="AG3">
-        <v>0.861</v>
+        <v>0.8595</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -993,22 +996,22 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>0.2402</v>
+        <v>0.2383</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="P4">
         <v>4.15</v>
       </c>
       <c r="Q4">
-        <v>0.1429</v>
+        <v>0.14</v>
       </c>
       <c r="R4">
-        <v>0.313</v>
+        <v>0.333</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
@@ -1026,7 +1029,7 @@
         <v>0.2319</v>
       </c>
       <c r="X4">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y4">
         <v>0.916</v>
@@ -1038,22 +1041,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.2097</v>
+        <v>0.2055</v>
       </c>
       <c r="AG4">
-        <v>0.9899</v>
+        <v>0.9882</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1082,7 +1085,7 @@
         <v>42</v>
       </c>
       <c r="I5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1094,22 +1097,22 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>0.18</v>
+        <v>0.181</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="P5">
-        <v>4.11</v>
+        <v>4.12</v>
       </c>
       <c r="Q5">
-        <v>0.1579</v>
+        <v>0.1667</v>
       </c>
       <c r="R5">
-        <v>0.363</v>
+        <v>0.398</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
@@ -1127,7 +1130,7 @@
         <v>0.2142</v>
       </c>
       <c r="X5">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y5">
         <v>0.9965</v>
@@ -1139,22 +1142,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>3.89</v>
+        <v>4.05</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.172</v>
+        <v>0.1753</v>
       </c>
       <c r="AG5">
-        <v>0.8598</v>
+        <v>0.8582</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>3.89</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1183,7 +1186,7 @@
         <v>42</v>
       </c>
       <c r="I6">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1195,22 +1198,22 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>0.1607</v>
+        <v>0.1606</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="P6">
-        <v>4.44</v>
+        <v>4.46</v>
       </c>
       <c r="Q6">
-        <v>0.1193</v>
+        <v>0.125</v>
       </c>
       <c r="R6">
-        <v>0.353</v>
+        <v>0.39</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
@@ -1228,7 +1231,7 @@
         <v>0.2071</v>
       </c>
       <c r="X6">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y6">
         <v>0.9728</v>
@@ -1240,22 +1243,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.1461</v>
+        <v>0.1467</v>
       </c>
       <c r="AG6">
-        <v>0.952</v>
+        <v>0.9503</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1284,7 +1287,7 @@
         <v>42</v>
       </c>
       <c r="I7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1296,22 +1299,22 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>0.2684</v>
+        <v>0.2708</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="P7">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="Q7">
-        <v>0.3148</v>
+        <v>0.3223</v>
       </c>
       <c r="R7">
-        <v>0.351</v>
+        <v>0.377</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
@@ -1329,7 +1332,7 @@
         <v>0.2185</v>
       </c>
       <c r="X7">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y7">
         <v>1.0261</v>
@@ -1341,22 +1344,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>7.08</v>
+        <v>7.36</v>
       </c>
       <c r="AE7" t="s">
         <v>53</v>
       </c>
       <c r="AF7">
-        <v>0.2847</v>
+        <v>0.2902</v>
       </c>
       <c r="AG7">
-        <v>1.1104</v>
+        <v>1.1084</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>7.08</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1385,7 +1388,7 @@
         <v>42</v>
       </c>
       <c r="I8">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1397,22 +1400,22 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.2064</v>
+        <v>0.2081</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="P8">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="Q8">
-        <v>0.1966</v>
+        <v>0.1944</v>
       </c>
       <c r="R8">
-        <v>0.369</v>
+        <v>0.351</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
@@ -1430,7 +1433,7 @@
         <v>0.2371</v>
       </c>
       <c r="X8">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y8">
         <v>1.0901</v>
@@ -1442,22 +1445,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>5.26</v>
+        <v>5.21</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.2028</v>
+        <v>0.2033</v>
       </c>
       <c r="AG8">
-        <v>1.107</v>
+        <v>1.105</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>5.26</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1498,10 +1501,22 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>0.2394</v>
+        <v>0.2065</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>21</v>
       </c>
       <c r="P9">
-        <v>4.44</v>
+        <v>4.8</v>
+      </c>
+      <c r="Q9">
+        <v>0.0952</v>
+      </c>
+      <c r="R9">
+        <v>0.095</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
@@ -1519,7 +1534,7 @@
         <v>0.2244</v>
       </c>
       <c r="X9">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y9">
         <v>1.0766</v>
@@ -1531,22 +1546,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>6.31</v>
+        <v>5.58</v>
       </c>
       <c r="AE9" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.2394</v>
+        <v>0.1959</v>
       </c>
       <c r="AG9">
-        <v>1.1033</v>
+        <v>1.1014</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>6.31</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1554,7 +1569,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10">
         <v>7.5</v>
@@ -1566,7 +1581,7 @@
         <v>-150</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>823992</v>
@@ -1620,7 +1635,7 @@
         <v>0.2537</v>
       </c>
       <c r="X10">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y10">
         <v>1.0953</v>
@@ -1632,7 +1647,7 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>9.95</v>
+        <v>9.93</v>
       </c>
       <c r="AE10" t="s">
         <v>53</v>
@@ -1641,13 +1656,13 @@
         <v>0.2699</v>
       </c>
       <c r="AG10">
-        <v>1.4234</v>
+        <v>1.4208</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>9.95</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1655,7 +1670,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11">
         <v>4.5</v>
@@ -1667,13 +1682,13 @@
         <v>-147</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>823992</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I11">
         <v>4.3</v>
@@ -1721,7 +1736,7 @@
         <v>0.2111</v>
       </c>
       <c r="X11">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y11">
         <v>0.88</v>
@@ -1742,7 +1757,7 @@
         <v>0.2079</v>
       </c>
       <c r="AG11">
-        <v>0.72</v>
+        <v>0.7187</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -1756,7 +1771,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1768,7 +1783,7 @@
         <v>-105</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G12">
         <v>825041</v>
@@ -1822,7 +1837,7 @@
         <v>0.1974</v>
       </c>
       <c r="X12">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y12">
         <v>0.88</v>
@@ -1834,7 +1849,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
@@ -1843,13 +1858,13 @@
         <v>0.2294</v>
       </c>
       <c r="AG12">
-        <v>0.7994</v>
+        <v>0.798</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1857,7 +1872,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C13">
         <v>3.5</v>
@@ -1869,7 +1884,7 @@
         <v>114</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G13">
         <v>825041</v>
@@ -1923,7 +1938,7 @@
         <v>0.2186</v>
       </c>
       <c r="X13">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y13">
         <v>0.9794</v>
@@ -1935,7 +1950,7 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
@@ -1944,13 +1959,13 @@
         <v>0.1552</v>
       </c>
       <c r="AG13">
-        <v>1.0085</v>
+        <v>1.0067</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1958,7 +1973,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -1970,7 +1985,7 @@
         <v>-150</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>823260</v>
@@ -2024,7 +2039,7 @@
         <v>0.2161</v>
       </c>
       <c r="X14">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y14">
         <v>1.0085</v>
@@ -2036,7 +2051,7 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
@@ -2045,13 +2060,13 @@
         <v>0.2549</v>
       </c>
       <c r="AG14">
-        <v>0.8556</v>
+        <v>0.8541</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2059,7 +2074,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C15">
         <v>5.5</v>
@@ -2071,7 +2086,7 @@
         <v>-102</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>823260</v>
@@ -2125,7 +2140,7 @@
         <v>0.259</v>
       </c>
       <c r="X15">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y15">
         <v>1.0952</v>
@@ -2137,22 +2152,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>6.3</v>
+        <v>6.28</v>
       </c>
       <c r="AE15" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="AF15">
         <v>0.1964</v>
       </c>
       <c r="AG15">
-        <v>1.2737</v>
+        <v>1.2714</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>6.3</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2226,7 +2241,7 @@
         <v>0.2138</v>
       </c>
       <c r="X16">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y16">
         <v>1.0204</v>
@@ -2238,7 +2253,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
@@ -2247,13 +2262,13 @@
         <v>0.1997</v>
       </c>
       <c r="AG16">
-        <v>0.9479</v>
+        <v>0.9462</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2327,7 +2342,7 @@
         <v>0.221</v>
       </c>
       <c r="X17">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y17">
         <v>0.9436</v>
@@ -2348,7 +2363,7 @@
         <v>0.1501</v>
       </c>
       <c r="AG17">
-        <v>0.8895</v>
+        <v>0.8879</v>
       </c>
       <c r="AH17">
         <v>0</v>
@@ -2428,7 +2443,7 @@
         <v>0.2248</v>
       </c>
       <c r="X18">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y18">
         <v>0.9919</v>
@@ -2440,7 +2455,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>7.41</v>
+        <v>7.4</v>
       </c>
       <c r="AE18" t="s">
         <v>53</v>
@@ -2449,13 +2464,13 @@
         <v>0.2985</v>
       </c>
       <c r="AG18">
-        <v>1.1092</v>
+        <v>1.1072</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>7.41</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2529,7 +2544,7 @@
         <v>0.2199</v>
       </c>
       <c r="X19">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y19">
         <v>0.9256</v>
@@ -2541,7 +2556,7 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
@@ -2550,13 +2565,13 @@
         <v>0.2511</v>
       </c>
       <c r="AG19">
-        <v>0.6946</v>
+        <v>0.6934</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2615,25 +2630,25 @@
         <v>0.365</v>
       </c>
       <c r="S20" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="T20">
-        <v>0.2085</v>
+        <v>0.2163</v>
       </c>
       <c r="U20">
-        <v>0.2085</v>
+        <v>0.2119</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>0.2043</v>
       </c>
       <c r="X20">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y20">
-        <v>1.0236</v>
+        <v>0.9638</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2642,22 +2657,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>6.59</v>
+        <v>6.42</v>
       </c>
       <c r="AE20" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="AF20">
         <v>0.2953</v>
       </c>
       <c r="AG20">
-        <v>0.9541</v>
+        <v>0.988</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>6.59</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2665,7 +2680,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21">
         <v>4.5</v>
@@ -2731,7 +2746,7 @@
         <v>0.2504</v>
       </c>
       <c r="X21">
-        <v>0.2185</v>
+        <v>0.2189</v>
       </c>
       <c r="Y21">
         <v>1.0671</v>
@@ -2743,7 +2758,7 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
@@ -2752,13 +2767,13 @@
         <v>0.1533</v>
       </c>
       <c r="AG21">
-        <v>1.4694</v>
+        <v>1.4668</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2775,7 +2790,7 @@
         <v>824557</v>
       </c>
       <c r="H22" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="I22">
         <v>4.5</v>
@@ -2796,7 +2811,7 @@
         <v>4.44</v>
       </c>
       <c r="S22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T22">
         <v>0.2365</v>

--- a/data/k-props/2026-08-24.xlsx
+++ b/data/k-props/2026-08-24.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="84">
   <si>
     <t>date</t>
   </si>
@@ -145,15 +145,21 @@
     <t>lineup_unweighted_30d_posted</t>
   </si>
   <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Framber Valdez</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Framber Valdez</t>
-  </si>
-  <si>
     <t>Ranger Suarez</t>
   </si>
   <si>
@@ -163,6 +169,9 @@
     <t>Sandy Alcantara</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
     <t>Ryan Feltner</t>
   </si>
   <si>
@@ -185,6 +194,9 @@
   </si>
   <si>
     <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
   <si>
     <t>Parker Messick</t>
@@ -832,17 +844,23 @@
       <c r="Y2">
         <v>0.8829</v>
       </c>
+      <c r="Z2">
+        <v>5</v>
+      </c>
       <c r="AA2" t="s">
         <v>44</v>
       </c>
+      <c r="AB2">
+        <v>-0.99</v>
+      </c>
       <c r="AC2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD2">
         <v>4.51</v>
       </c>
       <c r="AE2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF2">
         <v>0.2669</v>
@@ -852,6 +870,18 @@
       </c>
       <c r="AH2">
         <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.49</v>
+      </c>
+      <c r="AJ2">
+        <v>0.49</v>
+      </c>
+      <c r="AK2">
+        <v>0.49</v>
+      </c>
+      <c r="AL2">
+        <v>0.49</v>
       </c>
       <c r="AM2">
         <v>4.51</v>
@@ -862,7 +892,7 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>3.5</v>
@@ -933,17 +963,23 @@
       <c r="Y3">
         <v>0.88</v>
       </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
       <c r="AA3" t="s">
         <v>44</v>
       </c>
+      <c r="AB3">
+        <v>-0.53</v>
+      </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD3">
         <v>2.97</v>
       </c>
       <c r="AE3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>0.1599</v>
@@ -953,6 +989,18 @@
       </c>
       <c r="AH3">
         <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>-2.97</v>
+      </c>
+      <c r="AJ3">
+        <v>2.97</v>
+      </c>
+      <c r="AK3">
+        <v>-2.97</v>
+      </c>
+      <c r="AL3">
+        <v>2.97</v>
       </c>
       <c r="AM3">
         <v>2.97</v>
@@ -963,7 +1011,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>4.5</v>
@@ -975,7 +1023,7 @@
         <v>110</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>823828</v>
@@ -1034,17 +1082,23 @@
       <c r="Y4">
         <v>0.916</v>
       </c>
+      <c r="Z4">
+        <v>4</v>
+      </c>
       <c r="AA4" t="s">
         <v>44</v>
       </c>
+      <c r="AB4">
+        <v>-0.53</v>
+      </c>
       <c r="AC4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD4">
         <v>3.97</v>
       </c>
       <c r="AE4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF4">
         <v>0.2055</v>
@@ -1054,6 +1108,18 @@
       </c>
       <c r="AH4">
         <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0.03</v>
+      </c>
+      <c r="AJ4">
+        <v>0.03</v>
+      </c>
+      <c r="AK4">
+        <v>0.03</v>
+      </c>
+      <c r="AL4">
+        <v>0.03</v>
       </c>
       <c r="AM4">
         <v>3.97</v>
@@ -1064,7 +1130,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -1076,7 +1142,7 @@
         <v>-125</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>823828</v>
@@ -1135,17 +1201,23 @@
       <c r="Y5">
         <v>0.9965</v>
       </c>
+      <c r="Z5">
+        <v>6</v>
+      </c>
       <c r="AA5" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB5">
+        <v>-0.45</v>
       </c>
       <c r="AC5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD5">
         <v>4.05</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF5">
         <v>0.1753</v>
@@ -1155,6 +1227,18 @@
       </c>
       <c r="AH5">
         <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>1.95</v>
+      </c>
+      <c r="AJ5">
+        <v>1.95</v>
+      </c>
+      <c r="AK5">
+        <v>1.95</v>
+      </c>
+      <c r="AL5">
+        <v>1.95</v>
       </c>
       <c r="AM5">
         <v>4.05</v>
@@ -1165,7 +1249,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C6">
         <v>3.5</v>
@@ -1177,7 +1261,7 @@
         <v>-101</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>822695</v>
@@ -1236,17 +1320,23 @@
       <c r="Y6">
         <v>0.9728</v>
       </c>
+      <c r="Z6">
+        <v>6</v>
+      </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB6">
+        <v>-0.54</v>
       </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD6">
         <v>2.96</v>
       </c>
       <c r="AE6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF6">
         <v>0.1467</v>
@@ -1256,6 +1346,18 @@
       </c>
       <c r="AH6">
         <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>3.04</v>
+      </c>
+      <c r="AJ6">
+        <v>3.04</v>
+      </c>
+      <c r="AK6">
+        <v>3.04</v>
+      </c>
+      <c r="AL6">
+        <v>3.04</v>
       </c>
       <c r="AM6">
         <v>2.96</v>
@@ -1266,7 +1368,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C7">
         <v>6.5</v>
@@ -1278,7 +1380,7 @@
         <v>-119</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>822695</v>
@@ -1337,17 +1439,23 @@
       <c r="Y7">
         <v>1.0261</v>
       </c>
+      <c r="Z7">
+        <v>7</v>
+      </c>
       <c r="AA7" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB7">
+        <v>0.86</v>
       </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD7">
         <v>7.36</v>
       </c>
       <c r="AE7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AF7">
         <v>0.2902</v>
@@ -1357,6 +1465,18 @@
       </c>
       <c r="AH7">
         <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>-0.36</v>
+      </c>
+      <c r="AJ7">
+        <v>0.36</v>
+      </c>
+      <c r="AK7">
+        <v>-0.36</v>
+      </c>
+      <c r="AL7">
+        <v>0.36</v>
       </c>
       <c r="AM7">
         <v>7.36</v>
@@ -1367,7 +1487,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C8">
         <v>4.5</v>
@@ -1379,7 +1499,7 @@
         <v>102</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>824557</v>
@@ -1438,17 +1558,23 @@
       <c r="Y8">
         <v>1.0901</v>
       </c>
+      <c r="Z8">
+        <v>8</v>
+      </c>
       <c r="AA8" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB8">
+        <v>0.71</v>
       </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD8">
         <v>5.21</v>
       </c>
       <c r="AE8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF8">
         <v>0.2033</v>
@@ -1458,6 +1584,18 @@
       </c>
       <c r="AH8">
         <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>2.79</v>
+      </c>
+      <c r="AJ8">
+        <v>2.79</v>
+      </c>
+      <c r="AK8">
+        <v>2.79</v>
+      </c>
+      <c r="AL8">
+        <v>2.79</v>
       </c>
       <c r="AM8">
         <v>5.21</v>
@@ -1468,7 +1606,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C9">
         <v>3.5</v>
@@ -1480,13 +1618,13 @@
         <v>122</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G9">
         <v>824557</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I9">
         <v>5</v>
@@ -1539,17 +1677,23 @@
       <c r="Y9">
         <v>1.0766</v>
       </c>
+      <c r="Z9">
+        <v>2</v>
+      </c>
       <c r="AA9" t="s">
         <v>44</v>
       </c>
+      <c r="AB9">
+        <v>2.08</v>
+      </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="AD9">
         <v>5.58</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF9">
         <v>0.1959</v>
@@ -1559,6 +1703,18 @@
       </c>
       <c r="AH9">
         <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>-3.58</v>
+      </c>
+      <c r="AJ9">
+        <v>3.58</v>
+      </c>
+      <c r="AK9">
+        <v>-3.58</v>
+      </c>
+      <c r="AL9">
+        <v>3.58</v>
       </c>
       <c r="AM9">
         <v>5.58</v>
@@ -1569,7 +1725,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C10">
         <v>7.5</v>
@@ -1581,7 +1737,7 @@
         <v>-150</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G10">
         <v>823992</v>
@@ -1640,17 +1796,23 @@
       <c r="Y10">
         <v>1.0953</v>
       </c>
+      <c r="Z10">
+        <v>4</v>
+      </c>
       <c r="AA10" t="s">
         <v>44</v>
       </c>
+      <c r="AB10">
+        <v>2.43</v>
+      </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="AD10">
         <v>9.93</v>
       </c>
       <c r="AE10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AF10">
         <v>0.2699</v>
@@ -1660,6 +1822,18 @@
       </c>
       <c r="AH10">
         <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>-5.93</v>
+      </c>
+      <c r="AJ10">
+        <v>5.93</v>
+      </c>
+      <c r="AK10">
+        <v>-5.93</v>
+      </c>
+      <c r="AL10">
+        <v>5.93</v>
       </c>
       <c r="AM10">
         <v>9.93</v>
@@ -1670,7 +1844,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C11">
         <v>4.5</v>
@@ -1682,13 +1856,13 @@
         <v>-147</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>823992</v>
       </c>
       <c r="H11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I11">
         <v>4.3</v>
@@ -1741,17 +1915,23 @@
       <c r="Y11">
         <v>0.88</v>
       </c>
+      <c r="Z11">
+        <v>3</v>
+      </c>
       <c r="AA11" t="s">
         <v>44</v>
       </c>
+      <c r="AB11">
+        <v>-1.84</v>
+      </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD11">
         <v>2.66</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF11">
         <v>0.2079</v>
@@ -1761,6 +1941,18 @@
       </c>
       <c r="AH11">
         <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0.34</v>
+      </c>
+      <c r="AJ11">
+        <v>0.34</v>
+      </c>
+      <c r="AK11">
+        <v>0.34</v>
+      </c>
+      <c r="AL11">
+        <v>0.34</v>
       </c>
       <c r="AM11">
         <v>2.66</v>
@@ -1771,7 +1963,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1783,7 +1975,7 @@
         <v>-105</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G12">
         <v>825041</v>
@@ -1842,17 +2034,23 @@
       <c r="Y12">
         <v>0.88</v>
       </c>
+      <c r="Z12">
+        <v>6</v>
+      </c>
       <c r="AA12" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB12">
+        <v>-0.73</v>
       </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="AD12">
         <v>3.77</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF12">
         <v>0.2294</v>
@@ -1862,6 +2060,18 @@
       </c>
       <c r="AH12">
         <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>2.23</v>
+      </c>
+      <c r="AJ12">
+        <v>2.23</v>
+      </c>
+      <c r="AK12">
+        <v>2.23</v>
+      </c>
+      <c r="AL12">
+        <v>2.23</v>
       </c>
       <c r="AM12">
         <v>3.77</v>
@@ -1872,7 +2082,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C13">
         <v>3.5</v>
@@ -1884,7 +2094,7 @@
         <v>114</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G13">
         <v>825041</v>
@@ -1943,17 +2153,23 @@
       <c r="Y13">
         <v>0.9794</v>
       </c>
+      <c r="Z13">
+        <v>4</v>
+      </c>
       <c r="AA13" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB13">
+        <v>0.26</v>
       </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD13">
         <v>3.76</v>
       </c>
       <c r="AE13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF13">
         <v>0.1552</v>
@@ -1963,6 +2179,18 @@
       </c>
       <c r="AH13">
         <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0.24</v>
+      </c>
+      <c r="AJ13">
+        <v>0.24</v>
+      </c>
+      <c r="AK13">
+        <v>0.24</v>
+      </c>
+      <c r="AL13">
+        <v>0.24</v>
       </c>
       <c r="AM13">
         <v>3.76</v>
@@ -1973,7 +2201,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -1985,7 +2213,7 @@
         <v>-150</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G14">
         <v>823260</v>
@@ -2044,17 +2272,23 @@
       <c r="Y14">
         <v>1.0085</v>
       </c>
+      <c r="Z14">
+        <v>2</v>
+      </c>
       <c r="AA14" t="s">
         <v>44</v>
       </c>
+      <c r="AB14">
+        <v>-0.21</v>
+      </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD14">
         <v>5.29</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF14">
         <v>0.2549</v>
@@ -2064,6 +2298,18 @@
       </c>
       <c r="AH14">
         <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>-3.29</v>
+      </c>
+      <c r="AJ14">
+        <v>3.29</v>
+      </c>
+      <c r="AK14">
+        <v>-3.29</v>
+      </c>
+      <c r="AL14">
+        <v>3.29</v>
       </c>
       <c r="AM14">
         <v>5.29</v>
@@ -2074,7 +2320,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C15">
         <v>5.5</v>
@@ -2086,7 +2332,7 @@
         <v>-102</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G15">
         <v>823260</v>
@@ -2145,17 +2391,23 @@
       <c r="Y15">
         <v>1.0952</v>
       </c>
+      <c r="Z15">
+        <v>5</v>
+      </c>
       <c r="AA15" t="s">
         <v>44</v>
       </c>
+      <c r="AB15">
+        <v>0.78</v>
+      </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="AD15">
         <v>6.28</v>
       </c>
       <c r="AE15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AF15">
         <v>0.1964</v>
@@ -2165,6 +2417,18 @@
       </c>
       <c r="AH15">
         <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>-1.28</v>
+      </c>
+      <c r="AJ15">
+        <v>1.28</v>
+      </c>
+      <c r="AK15">
+        <v>-1.28</v>
+      </c>
+      <c r="AL15">
+        <v>1.28</v>
       </c>
       <c r="AM15">
         <v>6.28</v>
@@ -2175,7 +2439,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C16">
         <v>4.5</v>
@@ -2187,7 +2451,7 @@
         <v>-148</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G16">
         <v>824964</v>
@@ -2246,17 +2510,23 @@
       <c r="Y16">
         <v>1.0204</v>
       </c>
+      <c r="Z16">
+        <v>7</v>
+      </c>
       <c r="AA16" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="AB16">
+        <v>0.15</v>
       </c>
       <c r="AC16" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD16">
         <v>4.65</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF16">
         <v>0.1997</v>
@@ -2266,6 +2536,18 @@
       </c>
       <c r="AH16">
         <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>2.35</v>
+      </c>
+      <c r="AJ16">
+        <v>2.35</v>
+      </c>
+      <c r="AK16">
+        <v>2.35</v>
+      </c>
+      <c r="AL16">
+        <v>2.35</v>
       </c>
       <c r="AM16">
         <v>4.65</v>
@@ -2276,7 +2558,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C17">
         <v>3.5</v>
@@ -2288,7 +2570,7 @@
         <v>115</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G17">
         <v>824964</v>
@@ -2347,17 +2629,23 @@
       <c r="Y17">
         <v>0.9436</v>
       </c>
+      <c r="Z17">
+        <v>3</v>
+      </c>
       <c r="AA17" t="s">
         <v>44</v>
       </c>
+      <c r="AB17">
+        <v>-0.74</v>
+      </c>
       <c r="AC17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD17">
         <v>2.76</v>
       </c>
       <c r="AE17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF17">
         <v>0.1501</v>
@@ -2367,6 +2655,18 @@
       </c>
       <c r="AH17">
         <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0.24</v>
+      </c>
+      <c r="AJ17">
+        <v>0.24</v>
+      </c>
+      <c r="AK17">
+        <v>0.24</v>
+      </c>
+      <c r="AL17">
+        <v>0.24</v>
       </c>
       <c r="AM17">
         <v>2.76</v>
@@ -2377,7 +2677,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C18">
         <v>7.5</v>
@@ -2389,7 +2689,7 @@
         <v>-148</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G18">
         <v>823097</v>
@@ -2448,17 +2748,23 @@
       <c r="Y18">
         <v>0.9919</v>
       </c>
+      <c r="Z18">
+        <v>4</v>
+      </c>
       <c r="AA18" t="s">
         <v>44</v>
       </c>
+      <c r="AB18">
+        <v>-0.1</v>
+      </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD18">
         <v>7.4</v>
       </c>
       <c r="AE18" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AF18">
         <v>0.2985</v>
@@ -2468,6 +2774,18 @@
       </c>
       <c r="AH18">
         <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>-3.4</v>
+      </c>
+      <c r="AJ18">
+        <v>3.4</v>
+      </c>
+      <c r="AK18">
+        <v>-3.4</v>
+      </c>
+      <c r="AL18">
+        <v>3.4</v>
       </c>
       <c r="AM18">
         <v>7.4</v>
@@ -2478,7 +2796,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C19">
         <v>6.5</v>
@@ -2490,7 +2808,7 @@
         <v>-140</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G19">
         <v>823097</v>
@@ -2549,17 +2867,23 @@
       <c r="Y19">
         <v>0.9256</v>
       </c>
+      <c r="Z19">
+        <v>5</v>
+      </c>
       <c r="AA19" t="s">
         <v>44</v>
       </c>
+      <c r="AB19">
+        <v>-2.67</v>
+      </c>
       <c r="AC19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD19">
         <v>3.83</v>
       </c>
       <c r="AE19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF19">
         <v>0.2511</v>
@@ -2569,6 +2893,18 @@
       </c>
       <c r="AH19">
         <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>1.17</v>
+      </c>
+      <c r="AJ19">
+        <v>1.17</v>
+      </c>
+      <c r="AK19">
+        <v>1.17</v>
+      </c>
+      <c r="AL19">
+        <v>1.17</v>
       </c>
       <c r="AM19">
         <v>3.83</v>
@@ -2579,7 +2915,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C20">
         <v>6.5</v>
@@ -2591,7 +2927,7 @@
         <v>-115</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G20">
         <v>823183</v>
@@ -2650,17 +2986,23 @@
       <c r="Y20">
         <v>0.9638</v>
       </c>
+      <c r="Z20">
+        <v>5</v>
+      </c>
       <c r="AA20" t="s">
         <v>44</v>
       </c>
+      <c r="AB20">
+        <v>-0.08</v>
+      </c>
       <c r="AC20" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD20">
         <v>6.42</v>
       </c>
       <c r="AE20" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AF20">
         <v>0.2953</v>
@@ -2670,6 +3012,18 @@
       </c>
       <c r="AH20">
         <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>-1.42</v>
+      </c>
+      <c r="AJ20">
+        <v>1.42</v>
+      </c>
+      <c r="AK20">
+        <v>-1.42</v>
+      </c>
+      <c r="AL20">
+        <v>1.42</v>
       </c>
       <c r="AM20">
         <v>6.42</v>
@@ -2680,7 +3034,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C21">
         <v>4.5</v>
@@ -2692,7 +3046,7 @@
         <v>-117</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G21">
         <v>823183</v>
@@ -2751,17 +3105,23 @@
       <c r="Y21">
         <v>1.0671</v>
       </c>
+      <c r="Z21">
+        <v>3</v>
+      </c>
       <c r="AA21" t="s">
         <v>44</v>
       </c>
+      <c r="AB21">
+        <v>0.74</v>
+      </c>
       <c r="AC21" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="AD21">
         <v>5.24</v>
       </c>
       <c r="AE21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF21">
         <v>0.1533</v>
@@ -2771,6 +3131,18 @@
       </c>
       <c r="AH21">
         <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>-2.24</v>
+      </c>
+      <c r="AJ21">
+        <v>2.24</v>
+      </c>
+      <c r="AK21">
+        <v>-2.24</v>
+      </c>
+      <c r="AL21">
+        <v>2.24</v>
       </c>
       <c r="AM21">
         <v>5.24</v>
@@ -2781,16 +3153,16 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G22">
         <v>824557</v>
       </c>
       <c r="H22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I22">
         <v>4.5</v>
@@ -2811,7 +3183,7 @@
         <v>4.44</v>
       </c>
       <c r="S22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="T22">
         <v>0.2365</v>
@@ -2831,17 +3203,23 @@
       <c r="Y22">
         <v>1.0354</v>
       </c>
+      <c r="Z22">
+        <v>2</v>
+      </c>
       <c r="AA22" t="s">
         <v>44</v>
       </c>
+      <c r="AB22">
+        <v>2.08</v>
+      </c>
       <c r="AC22" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="AD22">
         <v>5.49</v>
       </c>
       <c r="AE22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF22">
         <v>0.2394</v>
@@ -2851,6 +3229,18 @@
       </c>
       <c r="AH22">
         <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>-3.49</v>
+      </c>
+      <c r="AJ22">
+        <v>3.49</v>
+      </c>
+      <c r="AK22">
+        <v>-3.49</v>
+      </c>
+      <c r="AL22">
+        <v>3.49</v>
       </c>
       <c r="AM22">
         <v>5.49</v>
